--- a/data/Training_set_new_final.xlsx
+++ b/data/Training_set_new_final.xlsx
@@ -1,46 +1,1025 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView windowWidth="28800" windowHeight="11380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="206">
+  <si>
+    <t>Donor.ID</t>
+  </si>
+  <si>
+    <t>resp.pCR</t>
+  </si>
+  <si>
+    <t>RCB.score</t>
+  </si>
+  <si>
+    <t>RCB.category</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>T.stage</t>
+  </si>
+  <si>
+    <t>LN.status.at.diagnosis</t>
+  </si>
+  <si>
+    <t>Histology</t>
+  </si>
+  <si>
+    <t>ER.status</t>
+  </si>
+  <si>
+    <t>HER2.status</t>
+  </si>
+  <si>
+    <t>Grade.pre.NAT</t>
+  </si>
+  <si>
+    <t>Chemo.cycles</t>
+  </si>
+  <si>
+    <t>Number.of.LN.removed</t>
+  </si>
+  <si>
+    <t>ENSG00000197794</t>
+  </si>
+  <si>
+    <t>ENSG00000182885</t>
+  </si>
+  <si>
+    <t>ENSG00000165966</t>
+  </si>
+  <si>
+    <t>ENSG00000267288</t>
+  </si>
+  <si>
+    <t>ENSG00000259616</t>
+  </si>
+  <si>
+    <t>ENSG00000124678</t>
+  </si>
+  <si>
+    <t>ENSG00000259362</t>
+  </si>
+  <si>
+    <t>ENSG00000154645</t>
+  </si>
+  <si>
+    <t>ENSG00000221887</t>
+  </si>
+  <si>
+    <t>ENSG00000204666</t>
+  </si>
+  <si>
+    <t>ENSG00000254973</t>
+  </si>
+  <si>
+    <t>ENSG00000163331</t>
+  </si>
+  <si>
+    <t>ENSG00000171401</t>
+  </si>
+  <si>
+    <t>ENSG00000232044</t>
+  </si>
+  <si>
+    <t>ENSG00000101188</t>
+  </si>
+  <si>
+    <t>ENSG00000179796</t>
+  </si>
+  <si>
+    <t>ENSG00000100346</t>
+  </si>
+  <si>
+    <t>ENSG00000272622</t>
+  </si>
+  <si>
+    <t>ENSG00000242540</t>
+  </si>
+  <si>
+    <t>ENSG00000005421</t>
+  </si>
+  <si>
+    <t>Coding.TMB</t>
+  </si>
+  <si>
+    <t>CodingMuts.PIK3CA</t>
+  </si>
+  <si>
+    <t>CodingMuts.TP53</t>
+  </si>
+  <si>
+    <t>CodingMuts.DNAH8</t>
+  </si>
+  <si>
+    <t>CodingMuts.LYST</t>
+  </si>
+  <si>
+    <t>CodingMuts.COL5A1</t>
+  </si>
+  <si>
+    <t>CIN.Prop</t>
+  </si>
+  <si>
+    <t>Expressed.NAg</t>
+  </si>
+  <si>
+    <t>HRD.sum</t>
+  </si>
+  <si>
+    <t>T001</t>
+  </si>
+  <si>
+    <t>RCB-I</t>
+  </si>
+  <si>
+    <t>T002</t>
+  </si>
+  <si>
+    <t>pCR</t>
+  </si>
+  <si>
+    <t>T003</t>
+  </si>
+  <si>
+    <t>T004</t>
+  </si>
+  <si>
+    <t>RCB-II</t>
+  </si>
+  <si>
+    <t>T005</t>
+  </si>
+  <si>
+    <t>T006</t>
+  </si>
+  <si>
+    <t>RCB-III</t>
+  </si>
+  <si>
+    <t>T007</t>
+  </si>
+  <si>
+    <t>T008</t>
+  </si>
+  <si>
+    <t>T009</t>
+  </si>
+  <si>
+    <t>T010</t>
+  </si>
+  <si>
+    <t>T011</t>
+  </si>
+  <si>
+    <t>T012</t>
+  </si>
+  <si>
+    <t>T013</t>
+  </si>
+  <si>
+    <t>T014</t>
+  </si>
+  <si>
+    <t>T015</t>
+  </si>
+  <si>
+    <t>T016</t>
+  </si>
+  <si>
+    <t>T017</t>
+  </si>
+  <si>
+    <t>T019</t>
+  </si>
+  <si>
+    <t>T020</t>
+  </si>
+  <si>
+    <t>T022</t>
+  </si>
+  <si>
+    <t>T023</t>
+  </si>
+  <si>
+    <t>T024</t>
+  </si>
+  <si>
+    <t>T025</t>
+  </si>
+  <si>
+    <t>T026</t>
+  </si>
+  <si>
+    <t>T028</t>
+  </si>
+  <si>
+    <t>T029</t>
+  </si>
+  <si>
+    <t>T030</t>
+  </si>
+  <si>
+    <t>T031</t>
+  </si>
+  <si>
+    <t>T032</t>
+  </si>
+  <si>
+    <t>T033</t>
+  </si>
+  <si>
+    <t>T035</t>
+  </si>
+  <si>
+    <t>T036</t>
+  </si>
+  <si>
+    <t>T037</t>
+  </si>
+  <si>
+    <t>T038</t>
+  </si>
+  <si>
+    <t>T039</t>
+  </si>
+  <si>
+    <t>T040</t>
+  </si>
+  <si>
+    <t>T041</t>
+  </si>
+  <si>
+    <t>T042</t>
+  </si>
+  <si>
+    <t>T043</t>
+  </si>
+  <si>
+    <t>T044</t>
+  </si>
+  <si>
+    <t>T045</t>
+  </si>
+  <si>
+    <t>T046</t>
+  </si>
+  <si>
+    <t>T047</t>
+  </si>
+  <si>
+    <t>T048</t>
+  </si>
+  <si>
+    <t>T049</t>
+  </si>
+  <si>
+    <t>T050</t>
+  </si>
+  <si>
+    <t>T051</t>
+  </si>
+  <si>
+    <t>T052</t>
+  </si>
+  <si>
+    <t>T053</t>
+  </si>
+  <si>
+    <t>T054</t>
+  </si>
+  <si>
+    <t>T055</t>
+  </si>
+  <si>
+    <t>T056</t>
+  </si>
+  <si>
+    <t>T057</t>
+  </si>
+  <si>
+    <t>T058</t>
+  </si>
+  <si>
+    <t>T059</t>
+  </si>
+  <si>
+    <t>T060</t>
+  </si>
+  <si>
+    <t>T061</t>
+  </si>
+  <si>
+    <t>T062</t>
+  </si>
+  <si>
+    <t>T064</t>
+  </si>
+  <si>
+    <t>T065</t>
+  </si>
+  <si>
+    <t>T066</t>
+  </si>
+  <si>
+    <t>T067</t>
+  </si>
+  <si>
+    <t>T068</t>
+  </si>
+  <si>
+    <t>T069</t>
+  </si>
+  <si>
+    <t>T070</t>
+  </si>
+  <si>
+    <t>T071</t>
+  </si>
+  <si>
+    <t>T072</t>
+  </si>
+  <si>
+    <t>T073</t>
+  </si>
+  <si>
+    <t>T074</t>
+  </si>
+  <si>
+    <t>T075</t>
+  </si>
+  <si>
+    <t>T076</t>
+  </si>
+  <si>
+    <t>T077</t>
+  </si>
+  <si>
+    <t>T078</t>
+  </si>
+  <si>
+    <t>T079</t>
+  </si>
+  <si>
+    <t>T080</t>
+  </si>
+  <si>
+    <t>T081</t>
+  </si>
+  <si>
+    <t>T083</t>
+  </si>
+  <si>
+    <t>T086</t>
+  </si>
+  <si>
+    <t>T087</t>
+  </si>
+  <si>
+    <t>T089</t>
+  </si>
+  <si>
+    <t>T090</t>
+  </si>
+  <si>
+    <t>T091</t>
+  </si>
+  <si>
+    <t>T092</t>
+  </si>
+  <si>
+    <t>T093</t>
+  </si>
+  <si>
+    <t>T094</t>
+  </si>
+  <si>
+    <t>T095</t>
+  </si>
+  <si>
+    <t>T096</t>
+  </si>
+  <si>
+    <t>T097</t>
+  </si>
+  <si>
+    <t>T098</t>
+  </si>
+  <si>
+    <t>T099</t>
+  </si>
+  <si>
+    <t>T100</t>
+  </si>
+  <si>
+    <t>T101</t>
+  </si>
+  <si>
+    <t>T102</t>
+  </si>
+  <si>
+    <t>T103</t>
+  </si>
+  <si>
+    <t>T104</t>
+  </si>
+  <si>
+    <t>T105</t>
+  </si>
+  <si>
+    <t>T109</t>
+  </si>
+  <si>
+    <t>T110</t>
+  </si>
+  <si>
+    <t>T112</t>
+  </si>
+  <si>
+    <t>T114</t>
+  </si>
+  <si>
+    <t>T115</t>
+  </si>
+  <si>
+    <t>T116</t>
+  </si>
+  <si>
+    <t>T117</t>
+  </si>
+  <si>
+    <t>T118</t>
+  </si>
+  <si>
+    <t>T119</t>
+  </si>
+  <si>
+    <t>T120</t>
+  </si>
+  <si>
+    <t>T121</t>
+  </si>
+  <si>
+    <t>T122</t>
+  </si>
+  <si>
+    <t>T123</t>
+  </si>
+  <si>
+    <t>T124</t>
+  </si>
+  <si>
+    <t>T125</t>
+  </si>
+  <si>
+    <t>T126</t>
+  </si>
+  <si>
+    <t>T127</t>
+  </si>
+  <si>
+    <t>T128</t>
+  </si>
+  <si>
+    <t>T129</t>
+  </si>
+  <si>
+    <t>T130</t>
+  </si>
+  <si>
+    <t>T131</t>
+  </si>
+  <si>
+    <t>T132</t>
+  </si>
+  <si>
+    <t>T133</t>
+  </si>
+  <si>
+    <t>T134</t>
+  </si>
+  <si>
+    <t>T135</t>
+  </si>
+  <si>
+    <t>T136</t>
+  </si>
+  <si>
+    <t>T137</t>
+  </si>
+  <si>
+    <t>T138</t>
+  </si>
+  <si>
+    <t>T139</t>
+  </si>
+  <si>
+    <t>T140</t>
+  </si>
+  <si>
+    <t>T141</t>
+  </si>
+  <si>
+    <t>T142</t>
+  </si>
+  <si>
+    <t>T143</t>
+  </si>
+  <si>
+    <t>T144</t>
+  </si>
+  <si>
+    <t>T145</t>
+  </si>
+  <si>
+    <t>T147</t>
+  </si>
+  <si>
+    <t>T148</t>
+  </si>
+  <si>
+    <t>T149</t>
+  </si>
+  <si>
+    <t>T150</t>
+  </si>
+  <si>
+    <t>T151</t>
+  </si>
+  <si>
+    <t>T152</t>
+  </si>
+  <si>
+    <t>T153</t>
+  </si>
+  <si>
+    <t>T154</t>
+  </si>
+  <si>
+    <t>T155</t>
+  </si>
+  <si>
+    <t>T156</t>
+  </si>
+  <si>
+    <t>T159</t>
+  </si>
+  <si>
+    <t>T160</t>
+  </si>
+  <si>
+    <t>T161</t>
+  </si>
+  <si>
+    <t>T162</t>
+  </si>
+  <si>
+    <t>T163</t>
+  </si>
+  <si>
+    <t>T164</t>
+  </si>
+  <si>
+    <t>T166</t>
+  </si>
+  <si>
+    <t>T167</t>
+  </si>
+  <si>
+    <t>T168</t>
+  </si>
+  <si>
+    <t>T169</t>
+  </si>
+  <si>
+    <t>T170</t>
+  </si>
+  <si>
+    <t>T171</t>
+  </si>
+  <si>
+    <t>T172</t>
+  </si>
+  <si>
+    <t>T173</t>
+  </si>
+  <si>
+    <t>T174</t>
+  </si>
+  <si>
+    <t>T175</t>
+  </si>
+  <si>
+    <t>T176</t>
+  </si>
+  <si>
+    <t>T178</t>
+  </si>
+  <si>
+    <t>T180</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -48,9 +1027,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -58,11 +1279,63 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -345,247 +1618,146 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AS161"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AP161"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Donor.ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>resp.pCR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>RCB.score</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>RCB.category</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>T.stage</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LN.status.at.diagnosis</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Histology</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ER.status</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>HER2.status</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Grade.pre.NAT</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Chemo.cycles</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Number.of.LN.removed</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000197794</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000182885</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000165966</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000267288</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000259616</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000124678</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000259362</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000154645</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000221887</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000204666</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000254973</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000163331</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000171401</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000232044</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000101188</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000179796</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000100346</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000272622</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000242540</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>ENSG00000005421</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Coding.TMB</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>CodingMuts.PIK3CA</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>CodingMuts.TP53</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>CodingMuts.DNAH8</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>CodingMuts.LYST</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>CodingMuts.COL5A1</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>CIN.Prop</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>Expressed.NAg</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>HRD</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>Telomeric.AI</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>LST</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>HRD.sum</t>
-        </is>
+    <row r="1" s="1" customFormat="1" spans="1:42">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>T001</t>
-        </is>
+    <row r="2" spans="1:42">
+      <c r="A2" t="s">
+        <v>42</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -593,10 +1765,8 @@
       <c r="C2">
         <v>0.98</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D2" t="s">
+        <v>43</v>
       </c>
       <c r="E2">
         <v>51</v>
@@ -677,7 +1847,7 @@
         <v>7.09155547642265</v>
       </c>
       <c r="AE2">
-        <v>8.103750767483859</v>
+        <v>8.10375076748386</v>
       </c>
       <c r="AF2">
         <v>5.11013508029124</v>
@@ -710,23 +1880,12 @@
         <v>29</v>
       </c>
       <c r="AP2">
-        <v>4</v>
-      </c>
-      <c r="AQ2">
-        <v>13</v>
-      </c>
-      <c r="AR2">
-        <v>3</v>
-      </c>
-      <c r="AS2">
         <v>20</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>T002</t>
-        </is>
+    <row r="3" spans="1:42">
+      <c r="A3" t="s">
+        <v>44</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -734,10 +1893,8 @@
       <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D3" t="s">
+        <v>45</v>
       </c>
       <c r="E3">
         <v>42</v>
@@ -851,23 +2008,12 @@
         <v>13</v>
       </c>
       <c r="AP3">
-        <v>16</v>
-      </c>
-      <c r="AQ3">
-        <v>22</v>
-      </c>
-      <c r="AR3">
-        <v>25</v>
-      </c>
-      <c r="AS3">
         <v>63</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>T003</t>
-        </is>
+    <row r="4" spans="1:42">
+      <c r="A4" t="s">
+        <v>46</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -875,10 +2021,8 @@
       <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D4" t="s">
+        <v>45</v>
       </c>
       <c r="E4">
         <v>36</v>
@@ -992,23 +2136,12 @@
         <v>12</v>
       </c>
       <c r="AP4">
-        <v>8</v>
-      </c>
-      <c r="AQ4">
-        <v>14</v>
-      </c>
-      <c r="AR4">
-        <v>2</v>
-      </c>
-      <c r="AS4">
         <v>24</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>T004</t>
-        </is>
+    <row r="5" spans="1:42">
+      <c r="A5" t="s">
+        <v>47</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1016,10 +2149,8 @@
       <c r="C5">
         <v>2.075</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D5" t="s">
+        <v>48</v>
       </c>
       <c r="E5">
         <v>33</v>
@@ -1133,23 +2264,12 @@
         <v>17</v>
       </c>
       <c r="AP5">
-        <v>11</v>
-      </c>
-      <c r="AQ5">
-        <v>22</v>
-      </c>
-      <c r="AR5">
-        <v>6</v>
-      </c>
-      <c r="AS5">
         <v>39</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>T005</t>
-        </is>
+    <row r="6" spans="1:42">
+      <c r="A6" t="s">
+        <v>49</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1157,10 +2277,8 @@
       <c r="C6">
         <v>2.866</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D6" t="s">
+        <v>48</v>
       </c>
       <c r="E6">
         <v>49</v>
@@ -1238,7 +2356,7 @@
         <v>4.5198386371752</v>
       </c>
       <c r="AD6">
-        <v>9.366124581332119</v>
+        <v>9.36612458133212</v>
       </c>
       <c r="AE6">
         <v>6.61810547572994</v>
@@ -1274,23 +2392,12 @@
         <v>7</v>
       </c>
       <c r="AP6">
-        <v>10</v>
-      </c>
-      <c r="AQ6">
-        <v>15</v>
-      </c>
-      <c r="AR6">
-        <v>3</v>
-      </c>
-      <c r="AS6">
         <v>28</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>T006</t>
-        </is>
+    <row r="7" spans="1:42">
+      <c r="A7" t="s">
+        <v>50</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1298,10 +2405,8 @@
       <c r="C7">
         <v>3.584</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D7" t="s">
+        <v>51</v>
       </c>
       <c r="E7">
         <v>46</v>
@@ -1415,23 +2520,12 @@
         <v>7</v>
       </c>
       <c r="AP7">
-        <v>2</v>
-      </c>
-      <c r="AQ7">
-        <v>2</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
         <v>4</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>T007</t>
-        </is>
+    <row r="8" spans="1:42">
+      <c r="A8" t="s">
+        <v>52</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1439,10 +2533,8 @@
       <c r="C8">
         <v>1.267</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D8" t="s">
+        <v>43</v>
       </c>
       <c r="E8">
         <v>42</v>
@@ -1511,7 +2603,7 @@
         <v>5.15962805096234</v>
       </c>
       <c r="AA8">
-        <v>8.095170598312039</v>
+        <v>8.09517059831204</v>
       </c>
       <c r="AB8">
         <v>5.49745542290934</v>
@@ -1520,7 +2612,7 @@
         <v>6.10865044959968</v>
       </c>
       <c r="AD8">
-        <v>8.252550314895499</v>
+        <v>8.2525503148955</v>
       </c>
       <c r="AE8">
         <v>5.95914833790823</v>
@@ -1529,7 +2621,7 @@
         <v>6.08015322334761</v>
       </c>
       <c r="AG8">
-        <v>8.547834037574651</v>
+        <v>8.54783403757465</v>
       </c>
       <c r="AH8">
         <v>24</v>
@@ -1556,23 +2648,12 @@
         <v>2</v>
       </c>
       <c r="AP8">
-        <v>11</v>
-      </c>
-      <c r="AQ8">
-        <v>8</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
         <v>19</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>T008</t>
-        </is>
+    <row r="9" spans="1:42">
+      <c r="A9" t="s">
+        <v>53</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1580,10 +2661,8 @@
       <c r="C9">
         <v>1.948</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D9" t="s">
+        <v>48</v>
       </c>
       <c r="E9">
         <v>50</v>
@@ -1697,23 +2776,12 @@
         <v>1</v>
       </c>
       <c r="AP9">
-        <v>8</v>
-      </c>
-      <c r="AQ9">
-        <v>9</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
         <v>17</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>T009</t>
-        </is>
+    <row r="10" spans="1:42">
+      <c r="A10" t="s">
+        <v>54</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1721,10 +2789,8 @@
       <c r="C10">
         <v>0.676</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D10" t="s">
+        <v>43</v>
       </c>
       <c r="E10">
         <v>53</v>
@@ -1760,7 +2826,7 @@
         <v>6.30122032972467</v>
       </c>
       <c r="P10">
-        <v>8.040284394493019</v>
+        <v>8.04028439449302</v>
       </c>
       <c r="Q10">
         <v>6.63712600394902</v>
@@ -1811,7 +2877,7 @@
         <v>6.75674571419848</v>
       </c>
       <c r="AG10">
-        <v>9.020773166522339</v>
+        <v>9.02077316652234</v>
       </c>
       <c r="AH10">
         <v>213</v>
@@ -1838,23 +2904,12 @@
         <v>56</v>
       </c>
       <c r="AP10">
-        <v>8</v>
-      </c>
-      <c r="AQ10">
-        <v>15</v>
-      </c>
-      <c r="AR10">
-        <v>1</v>
-      </c>
-      <c r="AS10">
         <v>24</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>T010</t>
-        </is>
+    <row r="11" spans="1:42">
+      <c r="A11" t="s">
+        <v>55</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1862,10 +2917,8 @@
       <c r="C11">
         <v>1.807</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D11" t="s">
+        <v>48</v>
       </c>
       <c r="E11">
         <v>56</v>
@@ -1904,7 +2957,7 @@
         <v>8.68658379378792</v>
       </c>
       <c r="Q11">
-        <v>8.144110093630299</v>
+        <v>8.1441100936303</v>
       </c>
       <c r="R11">
         <v>5.25879916092721</v>
@@ -1979,23 +3032,12 @@
         <v>8</v>
       </c>
       <c r="AP11">
-        <v>6</v>
-      </c>
-      <c r="AQ11">
-        <v>19</v>
-      </c>
-      <c r="AR11">
-        <v>1</v>
-      </c>
-      <c r="AS11">
         <v>26</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>T011</t>
-        </is>
+    <row r="12" spans="1:42">
+      <c r="A12" t="s">
+        <v>56</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -2003,10 +3045,8 @@
       <c r="C12">
         <v>0.876</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D12" t="s">
+        <v>43</v>
       </c>
       <c r="E12">
         <v>53</v>
@@ -2120,23 +3160,12 @@
         <v>17</v>
       </c>
       <c r="AP12">
-        <v>9</v>
-      </c>
-      <c r="AQ12">
-        <v>20</v>
-      </c>
-      <c r="AR12">
-        <v>10</v>
-      </c>
-      <c r="AS12">
         <v>39</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>T012</t>
-        </is>
+    <row r="13" spans="1:42">
+      <c r="A13" t="s">
+        <v>57</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -2144,10 +3173,8 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D13" t="s">
+        <v>45</v>
       </c>
       <c r="E13">
         <v>33</v>
@@ -2261,23 +3288,12 @@
         <v>20</v>
       </c>
       <c r="AP13">
-        <v>15</v>
-      </c>
-      <c r="AQ13">
-        <v>21</v>
-      </c>
-      <c r="AR13">
-        <v>25</v>
-      </c>
-      <c r="AS13">
         <v>61</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>T013</t>
-        </is>
+    <row r="14" spans="1:42">
+      <c r="A14" t="s">
+        <v>58</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -2285,10 +3301,8 @@
       <c r="C14">
         <v>0</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D14" t="s">
+        <v>45</v>
       </c>
       <c r="E14">
         <v>33</v>
@@ -2321,7 +3335,7 @@
         <v>4.55074024512635</v>
       </c>
       <c r="O14">
-        <v>8.449858206630489</v>
+        <v>8.44985820663049</v>
       </c>
       <c r="P14">
         <v>5.28496027231777</v>
@@ -2339,7 +3353,7 @@
         <v>5.95750877267071</v>
       </c>
       <c r="U14">
-        <v>8.818243849188519</v>
+        <v>8.81824384918852</v>
       </c>
       <c r="V14">
         <v>6.63204188405105</v>
@@ -2402,23 +3416,12 @@
         <v>16</v>
       </c>
       <c r="AP14">
-        <v>12</v>
-      </c>
-      <c r="AQ14">
-        <v>20</v>
-      </c>
-      <c r="AR14">
-        <v>6</v>
-      </c>
-      <c r="AS14">
         <v>38</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>T014</t>
-        </is>
+    <row r="15" spans="1:42">
+      <c r="A15" t="s">
+        <v>59</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -2426,10 +3429,8 @@
       <c r="C15">
         <v>0</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D15" t="s">
+        <v>45</v>
       </c>
       <c r="E15">
         <v>40</v>
@@ -2543,23 +3544,12 @@
         <v>25</v>
       </c>
       <c r="AP15">
-        <v>5</v>
-      </c>
-      <c r="AQ15">
-        <v>17</v>
-      </c>
-      <c r="AR15">
-        <v>1</v>
-      </c>
-      <c r="AS15">
         <v>23</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>T015</t>
-        </is>
+    <row r="16" spans="1:42">
+      <c r="A16" t="s">
+        <v>60</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2567,10 +3557,8 @@
       <c r="C16">
         <v>1.508</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D16" t="s">
+        <v>48</v>
       </c>
       <c r="E16">
         <v>57</v>
@@ -2684,23 +3672,12 @@
         <v>26</v>
       </c>
       <c r="AP16">
-        <v>3</v>
-      </c>
-      <c r="AQ16">
-        <v>14</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
         <v>17</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>T016</t>
-        </is>
+    <row r="17" spans="1:42">
+      <c r="A17" t="s">
+        <v>61</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2708,10 +3685,8 @@
       <c r="C17">
         <v>3.773</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D17" t="s">
+        <v>51</v>
       </c>
       <c r="E17">
         <v>56</v>
@@ -2825,23 +3800,12 @@
         <v>8</v>
       </c>
       <c r="AP17">
-        <v>3</v>
-      </c>
-      <c r="AQ17">
-        <v>9</v>
-      </c>
-      <c r="AR17">
-        <v>1</v>
-      </c>
-      <c r="AS17">
         <v>13</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>T017</t>
-        </is>
+    <row r="18" spans="1:42">
+      <c r="A18" t="s">
+        <v>62</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2849,10 +3813,8 @@
       <c r="C18">
         <v>2.403</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D18" t="s">
+        <v>48</v>
       </c>
       <c r="E18">
         <v>46</v>
@@ -2930,7 +3892,7 @@
         <v>6.9066173023421</v>
       </c>
       <c r="AD18">
-        <v>9.270381620370999</v>
+        <v>9.270381620371</v>
       </c>
       <c r="AE18">
         <v>6.72253938978434</v>
@@ -2966,23 +3928,12 @@
         <v>2</v>
       </c>
       <c r="AP18">
-        <v>8</v>
-      </c>
-      <c r="AQ18">
-        <v>6</v>
-      </c>
-      <c r="AR18">
-        <v>0</v>
-      </c>
-      <c r="AS18">
         <v>14</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>T019</t>
-        </is>
+    <row r="19" spans="1:42">
+      <c r="A19" t="s">
+        <v>63</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2990,10 +3941,8 @@
       <c r="C19">
         <v>3.359</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D19" t="s">
+        <v>51</v>
       </c>
       <c r="E19">
         <v>59</v>
@@ -3047,23 +3996,12 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>8</v>
-      </c>
-      <c r="AQ19">
-        <v>20</v>
-      </c>
-      <c r="AR19">
-        <v>1</v>
-      </c>
-      <c r="AS19">
         <v>29</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>T020</t>
-        </is>
+    <row r="20" spans="1:42">
+      <c r="A20" t="s">
+        <v>64</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3071,10 +4009,8 @@
       <c r="C20">
         <v>0.581</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D20" t="s">
+        <v>43</v>
       </c>
       <c r="E20">
         <v>34</v>
@@ -3152,7 +4088,7 @@
         <v>4.62588773474932</v>
       </c>
       <c r="AD20">
-        <v>8.476251064718131</v>
+        <v>8.47625106471813</v>
       </c>
       <c r="AE20">
         <v>6.67655559477297</v>
@@ -3188,23 +4124,12 @@
         <v>7</v>
       </c>
       <c r="AP20">
-        <v>5</v>
-      </c>
-      <c r="AQ20">
-        <v>8</v>
-      </c>
-      <c r="AR20">
-        <v>1</v>
-      </c>
-      <c r="AS20">
         <v>14</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>T022</t>
-        </is>
+    <row r="21" spans="1:42">
+      <c r="A21" t="s">
+        <v>65</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -3212,10 +4137,8 @@
       <c r="C21">
         <v>0</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D21" t="s">
+        <v>45</v>
       </c>
       <c r="E21">
         <v>42</v>
@@ -3329,23 +4252,12 @@
         <v>6</v>
       </c>
       <c r="AP21">
-        <v>3</v>
-      </c>
-      <c r="AQ21">
-        <v>13</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
         <v>16</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>T023</t>
-        </is>
+    <row r="22" spans="1:42">
+      <c r="A22" t="s">
+        <v>66</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3353,10 +4265,8 @@
       <c r="C22">
         <v>2.474</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D22" t="s">
+        <v>48</v>
       </c>
       <c r="E22">
         <v>39</v>
@@ -3470,23 +4380,12 @@
         <v>2</v>
       </c>
       <c r="AP22">
-        <v>1</v>
-      </c>
-      <c r="AQ22">
-        <v>4</v>
-      </c>
-      <c r="AR22">
-        <v>0</v>
-      </c>
-      <c r="AS22">
         <v>5</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>T024</t>
-        </is>
+    <row r="23" spans="1:42">
+      <c r="A23" t="s">
+        <v>67</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -3494,10 +4393,8 @@
       <c r="C23">
         <v>0</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D23" t="s">
+        <v>45</v>
       </c>
       <c r="E23">
         <v>27</v>
@@ -3548,7 +4445,7 @@
         <v>5.16428827858061</v>
       </c>
       <c r="U23">
-        <v>8.849992600282389</v>
+        <v>8.84999260028239</v>
       </c>
       <c r="V23">
         <v>7.22172456170196</v>
@@ -3611,23 +4508,12 @@
         <v>9</v>
       </c>
       <c r="AP23">
-        <v>4</v>
-      </c>
-      <c r="AQ23">
-        <v>17</v>
-      </c>
-      <c r="AR23">
-        <v>4</v>
-      </c>
-      <c r="AS23">
         <v>25</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>T025</t>
-        </is>
+    <row r="24" spans="1:42">
+      <c r="A24" t="s">
+        <v>68</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3635,10 +4521,8 @@
       <c r="C24">
         <v>3.828</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D24" t="s">
+        <v>51</v>
       </c>
       <c r="E24">
         <v>62</v>
@@ -3752,23 +4636,12 @@
         <v>8</v>
       </c>
       <c r="AP24">
-        <v>7</v>
-      </c>
-      <c r="AQ24">
-        <v>14</v>
-      </c>
-      <c r="AR24">
-        <v>1</v>
-      </c>
-      <c r="AS24">
         <v>22</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>T026</t>
-        </is>
+    <row r="25" spans="1:42">
+      <c r="A25" t="s">
+        <v>69</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3776,10 +4649,8 @@
       <c r="C25">
         <v>1.57</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D25" t="s">
+        <v>48</v>
       </c>
       <c r="E25">
         <v>32</v>
@@ -3830,7 +4701,7 @@
         <v>5.85236480814253</v>
       </c>
       <c r="U25">
-        <v>8.605447384824449</v>
+        <v>8.60544738482445</v>
       </c>
       <c r="V25">
         <v>5.59965911832282</v>
@@ -3893,23 +4764,12 @@
         <v>23</v>
       </c>
       <c r="AP25">
-        <v>11</v>
-      </c>
-      <c r="AQ25">
-        <v>18</v>
-      </c>
-      <c r="AR25">
-        <v>14</v>
-      </c>
-      <c r="AS25">
         <v>43</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>T028</t>
-        </is>
+    <row r="26" spans="1:42">
+      <c r="A26" t="s">
+        <v>70</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -3917,10 +4777,8 @@
       <c r="C26">
         <v>0</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D26" t="s">
+        <v>45</v>
       </c>
       <c r="E26">
         <v>37</v>
@@ -4034,23 +4892,12 @@
         <v>27</v>
       </c>
       <c r="AP26">
-        <v>7</v>
-      </c>
-      <c r="AQ26">
-        <v>8</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
         <v>15</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>T029</t>
-        </is>
+    <row r="27" spans="1:42">
+      <c r="A27" t="s">
+        <v>71</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -4058,10 +4905,8 @@
       <c r="C27">
         <v>2.066</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D27" t="s">
+        <v>48</v>
       </c>
       <c r="E27">
         <v>53</v>
@@ -4124,7 +4969,7 @@
         <v>6.64090526958423</v>
       </c>
       <c r="Y27">
-        <v>8.132338974988601</v>
+        <v>8.1323389749886</v>
       </c>
       <c r="Z27">
         <v>4.17134477173739</v>
@@ -4175,23 +5020,12 @@
         <v>6</v>
       </c>
       <c r="AP27">
-        <v>7</v>
-      </c>
-      <c r="AQ27">
-        <v>14</v>
-      </c>
-      <c r="AR27">
-        <v>2</v>
-      </c>
-      <c r="AS27">
         <v>23</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>T030</t>
-        </is>
+    <row r="28" spans="1:42">
+      <c r="A28" t="s">
+        <v>72</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -4199,10 +5033,8 @@
       <c r="C28">
         <v>1.613</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D28" t="s">
+        <v>48</v>
       </c>
       <c r="E28">
         <v>48</v>
@@ -4238,7 +5070,7 @@
         <v>6.58554451999156</v>
       </c>
       <c r="P28">
-        <v>8.361583122672499</v>
+        <v>8.3615831226725</v>
       </c>
       <c r="Q28">
         <v>6.6209612013822</v>
@@ -4280,7 +5112,7 @@
         <v>5.89187921610094</v>
       </c>
       <c r="AD28">
-        <v>8.166350458154049</v>
+        <v>8.16635045815405</v>
       </c>
       <c r="AE28">
         <v>6.97322075383274</v>
@@ -4316,23 +5148,12 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>8</v>
-      </c>
-      <c r="AQ28">
-        <v>12</v>
-      </c>
-      <c r="AR28">
-        <v>1</v>
-      </c>
-      <c r="AS28">
         <v>21</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>T031</t>
-        </is>
+    <row r="29" spans="1:42">
+      <c r="A29" t="s">
+        <v>73</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -4340,10 +5161,8 @@
       <c r="C29">
         <v>0</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D29" t="s">
+        <v>45</v>
       </c>
       <c r="E29">
         <v>51</v>
@@ -4376,7 +5195,7 @@
         <v>5.55421779474037</v>
       </c>
       <c r="O29">
-        <v>8.001410794134181</v>
+        <v>8.00141079413418</v>
       </c>
       <c r="P29">
         <v>6.7055741272181</v>
@@ -4457,23 +5276,12 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>8</v>
-      </c>
-      <c r="AQ29">
-        <v>8</v>
-      </c>
-      <c r="AR29">
-        <v>7</v>
-      </c>
-      <c r="AS29">
         <v>23</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>T032</t>
-        </is>
+    <row r="30" spans="1:42">
+      <c r="A30" t="s">
+        <v>74</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -4481,10 +5289,8 @@
       <c r="C30">
         <v>1.72</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D30" t="s">
+        <v>48</v>
       </c>
       <c r="E30">
         <v>69</v>
@@ -4592,29 +5398,18 @@
         <v>0</v>
       </c>
       <c r="AN30">
-        <v>0.6180323814833451</v>
+        <v>0.618032381483345</v>
       </c>
       <c r="AO30">
         <v>30</v>
       </c>
       <c r="AP30">
-        <v>20</v>
-      </c>
-      <c r="AQ30">
-        <v>29</v>
-      </c>
-      <c r="AR30">
-        <v>16</v>
-      </c>
-      <c r="AS30">
         <v>65</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>T033</t>
-        </is>
+    <row r="31" spans="1:42">
+      <c r="A31" t="s">
+        <v>75</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -4622,10 +5417,8 @@
       <c r="C31">
         <v>1.388</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D31" t="s">
+        <v>48</v>
       </c>
       <c r="E31">
         <v>49</v>
@@ -4703,7 +5496,7 @@
         <v>4.17134477173739</v>
       </c>
       <c r="AD31">
-        <v>9.504529035104641</v>
+        <v>9.50452903510464</v>
       </c>
       <c r="AE31">
         <v>7.24019980498089</v>
@@ -4739,23 +5532,12 @@
         <v>29</v>
       </c>
       <c r="AP31">
-        <v>21</v>
-      </c>
-      <c r="AQ31">
-        <v>21</v>
-      </c>
-      <c r="AR31">
-        <v>20</v>
-      </c>
-      <c r="AS31">
         <v>62</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>T035</t>
-        </is>
+    <row r="32" spans="1:42">
+      <c r="A32" t="s">
+        <v>76</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -4763,10 +5545,8 @@
       <c r="C32">
         <v>1.601</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D32" t="s">
+        <v>48</v>
       </c>
       <c r="E32">
         <v>33</v>
@@ -4829,7 +5609,7 @@
         <v>5.63561605725837</v>
       </c>
       <c r="Y32">
-        <v>8.897421497131569</v>
+        <v>8.89742149713157</v>
       </c>
       <c r="Z32">
         <v>6.04663796779609</v>
@@ -4880,23 +5660,12 @@
         <v>10</v>
       </c>
       <c r="AP32">
-        <v>11</v>
-      </c>
-      <c r="AQ32">
-        <v>22</v>
-      </c>
-      <c r="AR32">
-        <v>6</v>
-      </c>
-      <c r="AS32">
         <v>39</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>T036</t>
-        </is>
+    <row r="33" spans="1:42">
+      <c r="A33" t="s">
+        <v>77</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -4904,10 +5673,8 @@
       <c r="C33">
         <v>0</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D33" t="s">
+        <v>45</v>
       </c>
       <c r="E33">
         <v>54</v>
@@ -5021,23 +5788,12 @@
         <v>26</v>
       </c>
       <c r="AP33">
-        <v>13</v>
-      </c>
-      <c r="AQ33">
-        <v>19</v>
-      </c>
-      <c r="AR33">
-        <v>27</v>
-      </c>
-      <c r="AS33">
         <v>59</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>T037</t>
-        </is>
+    <row r="34" spans="1:42">
+      <c r="A34" t="s">
+        <v>78</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -5045,10 +5801,8 @@
       <c r="C34">
         <v>0</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D34" t="s">
+        <v>45</v>
       </c>
       <c r="E34">
         <v>49</v>
@@ -5162,23 +5916,12 @@
         <v>11</v>
       </c>
       <c r="AP34">
-        <v>8</v>
-      </c>
-      <c r="AQ34">
-        <v>25</v>
-      </c>
-      <c r="AR34">
-        <v>7</v>
-      </c>
-      <c r="AS34">
         <v>40</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>T038</t>
-        </is>
+    <row r="35" spans="1:42">
+      <c r="A35" t="s">
+        <v>79</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -5186,10 +5929,8 @@
       <c r="C35">
         <v>0</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D35" t="s">
+        <v>45</v>
       </c>
       <c r="E35">
         <v>41</v>
@@ -5267,7 +6008,7 @@
         <v>4.67695504333559</v>
       </c>
       <c r="AD35">
-        <v>8.593232681333109</v>
+        <v>8.59323268133311</v>
       </c>
       <c r="AE35">
         <v>6.38496868511301</v>
@@ -5303,23 +6044,12 @@
         <v>13</v>
       </c>
       <c r="AP35">
-        <v>10</v>
-      </c>
-      <c r="AQ35">
-        <v>23</v>
-      </c>
-      <c r="AR35">
-        <v>3</v>
-      </c>
-      <c r="AS35">
         <v>36</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>T039</t>
-        </is>
+    <row r="36" spans="1:42">
+      <c r="A36" t="s">
+        <v>80</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -5327,10 +6057,8 @@
       <c r="C36">
         <v>1.279</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D36" t="s">
+        <v>43</v>
       </c>
       <c r="E36">
         <v>51</v>
@@ -5366,7 +6094,7 @@
         <v>5.14634803859811</v>
       </c>
       <c r="P36">
-        <v>8.165161280398831</v>
+        <v>8.16516128039883</v>
       </c>
       <c r="Q36">
         <v>8.38835198009633</v>
@@ -5393,7 +6121,7 @@
         <v>6.12620503918325</v>
       </c>
       <c r="Y36">
-        <v>8.802305109682811</v>
+        <v>8.80230510968281</v>
       </c>
       <c r="Z36">
         <v>4.48495122695193</v>
@@ -5444,23 +6172,12 @@
         <v>9</v>
       </c>
       <c r="AP36">
-        <v>1</v>
-      </c>
-      <c r="AQ36">
-        <v>4</v>
-      </c>
-      <c r="AR36">
-        <v>0</v>
-      </c>
-      <c r="AS36">
         <v>5</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>T040</t>
-        </is>
+    <row r="37" spans="1:42">
+      <c r="A37" t="s">
+        <v>81</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -5468,10 +6185,8 @@
       <c r="C37">
         <v>0</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D37" t="s">
+        <v>45</v>
       </c>
       <c r="E37">
         <v>34</v>
@@ -5585,23 +6300,12 @@
         <v>9</v>
       </c>
       <c r="AP37">
-        <v>9</v>
-      </c>
-      <c r="AQ37">
-        <v>26</v>
-      </c>
-      <c r="AR37">
-        <v>2</v>
-      </c>
-      <c r="AS37">
         <v>37</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>T041</t>
-        </is>
+    <row r="38" spans="1:42">
+      <c r="A38" t="s">
+        <v>82</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -5609,10 +6313,8 @@
       <c r="C38">
         <v>2.068</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D38" t="s">
+        <v>48</v>
       </c>
       <c r="E38">
         <v>44</v>
@@ -5690,7 +6392,7 @@
         <v>4.50450824662369</v>
       </c>
       <c r="AD38">
-        <v>8.848504952466619</v>
+        <v>8.84850495246662</v>
       </c>
       <c r="AE38">
         <v>4.50450824662369</v>
@@ -5726,23 +6428,12 @@
         <v>9</v>
       </c>
       <c r="AP38">
-        <v>8</v>
-      </c>
-      <c r="AQ38">
-        <v>15</v>
-      </c>
-      <c r="AR38">
-        <v>8</v>
-      </c>
-      <c r="AS38">
         <v>31</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>T042</t>
-        </is>
+    <row r="39" spans="1:42">
+      <c r="A39" t="s">
+        <v>83</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -5750,10 +6441,8 @@
       <c r="C39">
         <v>0.892</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D39" t="s">
+        <v>43</v>
       </c>
       <c r="E39">
         <v>57</v>
@@ -5867,23 +6556,12 @@
         <v>13</v>
       </c>
       <c r="AP39">
-        <v>10</v>
-      </c>
-      <c r="AQ39">
-        <v>22</v>
-      </c>
-      <c r="AR39">
-        <v>16</v>
-      </c>
-      <c r="AS39">
         <v>48</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>T043</t>
-        </is>
+    <row r="40" spans="1:42">
+      <c r="A40" t="s">
+        <v>84</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -5891,10 +6569,8 @@
       <c r="C40">
         <v>3.65</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D40" t="s">
+        <v>51</v>
       </c>
       <c r="E40">
         <v>54</v>
@@ -5930,7 +6606,7 @@
         <v>6.5068654782443</v>
       </c>
       <c r="P40">
-        <v>9.398067307242981</v>
+        <v>9.39806730724298</v>
       </c>
       <c r="Q40">
         <v>6.9134033824026</v>
@@ -6008,23 +6684,12 @@
         <v>4</v>
       </c>
       <c r="AP40">
-        <v>2</v>
-      </c>
-      <c r="AQ40">
-        <v>8</v>
-      </c>
-      <c r="AR40">
-        <v>0</v>
-      </c>
-      <c r="AS40">
         <v>10</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>T044</t>
-        </is>
+    <row r="41" spans="1:42">
+      <c r="A41" t="s">
+        <v>85</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -6032,10 +6697,8 @@
       <c r="C41">
         <v>3.514</v>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D41" t="s">
+        <v>51</v>
       </c>
       <c r="E41">
         <v>40</v>
@@ -6149,34 +6812,21 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>6</v>
-      </c>
-      <c r="AQ41">
-        <v>8</v>
-      </c>
-      <c r="AR41">
-        <v>6</v>
-      </c>
-      <c r="AS41">
         <v>20</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>T045</t>
-        </is>
+    <row r="42" spans="1:42">
+      <c r="A42" t="s">
+        <v>86</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+        <v>0.69</v>
+      </c>
+      <c r="D42" t="s">
+        <v>43</v>
       </c>
       <c r="E42">
         <v>41</v>
@@ -6290,23 +6940,12 @@
         <v>5</v>
       </c>
       <c r="AP42">
-        <v>7</v>
-      </c>
-      <c r="AQ42">
-        <v>13</v>
-      </c>
-      <c r="AR42">
-        <v>0</v>
-      </c>
-      <c r="AS42">
         <v>20</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>T046</t>
-        </is>
+    <row r="43" spans="1:42">
+      <c r="A43" t="s">
+        <v>87</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -6314,10 +6953,8 @@
       <c r="C43">
         <v>2.873</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D43" t="s">
+        <v>48</v>
       </c>
       <c r="E43">
         <v>65</v>
@@ -6431,23 +7068,12 @@
         <v>8</v>
       </c>
       <c r="AP43">
-        <v>18</v>
-      </c>
-      <c r="AQ43">
-        <v>17</v>
-      </c>
-      <c r="AR43">
-        <v>10</v>
-      </c>
-      <c r="AS43">
         <v>45</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>T047</t>
-        </is>
+    <row r="44" spans="1:42">
+      <c r="A44" t="s">
+        <v>88</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -6455,10 +7081,8 @@
       <c r="C44">
         <v>2.795</v>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D44" t="s">
+        <v>48</v>
       </c>
       <c r="E44">
         <v>58</v>
@@ -6572,23 +7196,12 @@
         <v>8</v>
       </c>
       <c r="AP44">
-        <v>5</v>
-      </c>
-      <c r="AQ44">
-        <v>6</v>
-      </c>
-      <c r="AR44">
-        <v>5</v>
-      </c>
-      <c r="AS44">
         <v>16</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>T048</t>
-        </is>
+    <row r="45" spans="1:42">
+      <c r="A45" t="s">
+        <v>89</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -6596,10 +7209,8 @@
       <c r="C45">
         <v>1.354</v>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D45" t="s">
+        <v>43</v>
       </c>
       <c r="E45">
         <v>66</v>
@@ -6713,23 +7324,12 @@
         <v>19</v>
       </c>
       <c r="AP45">
-        <v>14</v>
-      </c>
-      <c r="AQ45">
-        <v>13</v>
-      </c>
-      <c r="AR45">
-        <v>7</v>
-      </c>
-      <c r="AS45">
         <v>34</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>T049</t>
-        </is>
+    <row r="46" spans="1:42">
+      <c r="A46" t="s">
+        <v>90</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -6737,10 +7337,8 @@
       <c r="C46">
         <v>0</v>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D46" t="s">
+        <v>45</v>
       </c>
       <c r="E46">
         <v>37</v>
@@ -6854,23 +7452,12 @@
         <v>5</v>
       </c>
       <c r="AP46">
-        <v>15</v>
-      </c>
-      <c r="AQ46">
-        <v>16</v>
-      </c>
-      <c r="AR46">
-        <v>15</v>
-      </c>
-      <c r="AS46">
         <v>46</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>T050</t>
-        </is>
+    <row r="47" spans="1:42">
+      <c r="A47" t="s">
+        <v>91</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -6878,10 +7465,8 @@
       <c r="C47">
         <v>3.615</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D47" t="s">
+        <v>51</v>
       </c>
       <c r="E47">
         <v>60</v>
@@ -6995,23 +7580,12 @@
         <v>7</v>
       </c>
       <c r="AP47">
-        <v>7</v>
-      </c>
-      <c r="AQ47">
-        <v>8</v>
-      </c>
-      <c r="AR47">
-        <v>0</v>
-      </c>
-      <c r="AS47">
         <v>15</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>T051</t>
-        </is>
+    <row r="48" spans="1:42">
+      <c r="A48" t="s">
+        <v>92</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -7019,10 +7593,8 @@
       <c r="C48">
         <v>1.595</v>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D48" t="s">
+        <v>48</v>
       </c>
       <c r="E48">
         <v>46</v>
@@ -7136,34 +7708,21 @@
         <v>4</v>
       </c>
       <c r="AP48">
-        <v>2</v>
-      </c>
-      <c r="AQ48">
-        <v>3</v>
-      </c>
-      <c r="AR48">
-        <v>0</v>
-      </c>
-      <c r="AS48">
         <v>5</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>T052</t>
-        </is>
+    <row r="49" spans="1:42">
+      <c r="A49" t="s">
+        <v>93</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+        <v>0.941</v>
+      </c>
+      <c r="D49" t="s">
+        <v>43</v>
       </c>
       <c r="E49">
         <v>35</v>
@@ -7277,23 +7836,12 @@
         <v>10</v>
       </c>
       <c r="AP49">
-        <v>4</v>
-      </c>
-      <c r="AQ49">
-        <v>11</v>
-      </c>
-      <c r="AR49">
-        <v>1</v>
-      </c>
-      <c r="AS49">
         <v>16</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>T053</t>
-        </is>
+    <row r="50" spans="1:42">
+      <c r="A50" t="s">
+        <v>94</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -7301,10 +7849,8 @@
       <c r="C50">
         <v>3.429</v>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D50" t="s">
+        <v>51</v>
       </c>
       <c r="E50">
         <v>46</v>
@@ -7358,23 +7904,12 @@
         <v>0</v>
       </c>
       <c r="AP50">
-        <v>8</v>
-      </c>
-      <c r="AQ50">
-        <v>8</v>
-      </c>
-      <c r="AR50">
-        <v>3</v>
-      </c>
-      <c r="AS50">
         <v>19</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>T054</t>
-        </is>
+    <row r="51" spans="1:42">
+      <c r="A51" t="s">
+        <v>95</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -7382,10 +7917,8 @@
       <c r="C51">
         <v>0</v>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D51" t="s">
+        <v>45</v>
       </c>
       <c r="E51">
         <v>51</v>
@@ -7421,7 +7954,7 @@
         <v>6.13330896115392</v>
       </c>
       <c r="P51">
-        <v>8.150033592380391</v>
+        <v>8.15003359238039</v>
       </c>
       <c r="Q51">
         <v>5.40941199327663</v>
@@ -7454,7 +7987,7 @@
         <v>4.68964466490062</v>
       </c>
       <c r="AA51">
-        <v>8.933802212673561</v>
+        <v>8.93380221267356</v>
       </c>
       <c r="AB51">
         <v>4.17134477173739</v>
@@ -7499,23 +8032,12 @@
         <v>11</v>
       </c>
       <c r="AP51">
-        <v>15</v>
-      </c>
-      <c r="AQ51">
-        <v>31</v>
-      </c>
-      <c r="AR51">
-        <v>9</v>
-      </c>
-      <c r="AS51">
         <v>55</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>T055</t>
-        </is>
+    <row r="52" spans="1:42">
+      <c r="A52" t="s">
+        <v>96</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -7523,10 +8045,8 @@
       <c r="C52">
         <v>2.368</v>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D52" t="s">
+        <v>48</v>
       </c>
       <c r="E52">
         <v>63</v>
@@ -7580,23 +8100,12 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>4</v>
-      </c>
-      <c r="AQ52">
-        <v>8</v>
-      </c>
-      <c r="AR52">
-        <v>1</v>
-      </c>
-      <c r="AS52">
         <v>13</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>T056</t>
-        </is>
+    <row r="53" spans="1:42">
+      <c r="A53" t="s">
+        <v>97</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -7604,10 +8113,8 @@
       <c r="C53">
         <v>1.92</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D53" t="s">
+        <v>48</v>
       </c>
       <c r="E53">
         <v>55</v>
@@ -7721,23 +8228,12 @@
         <v>3</v>
       </c>
       <c r="AP53">
-        <v>2</v>
-      </c>
-      <c r="AQ53">
-        <v>9</v>
-      </c>
-      <c r="AR53">
-        <v>0</v>
-      </c>
-      <c r="AS53">
         <v>11</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>T057</t>
-        </is>
+    <row r="54" spans="1:42">
+      <c r="A54" t="s">
+        <v>98</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -7745,10 +8241,8 @@
       <c r="C54">
         <v>0</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D54" t="s">
+        <v>45</v>
       </c>
       <c r="E54">
         <v>42</v>
@@ -7781,7 +8275,7 @@
         <v>4.17134477173739</v>
       </c>
       <c r="O54">
-        <v>8.100167699132349</v>
+        <v>8.10016769913235</v>
       </c>
       <c r="P54">
         <v>5.94591136612712</v>
@@ -7862,23 +8356,12 @@
         <v>13</v>
       </c>
       <c r="AP54">
-        <v>4</v>
-      </c>
-      <c r="AQ54">
-        <v>16</v>
-      </c>
-      <c r="AR54">
-        <v>4</v>
-      </c>
-      <c r="AS54">
         <v>24</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>T058</t>
-        </is>
+    <row r="55" spans="1:42">
+      <c r="A55" t="s">
+        <v>99</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -7886,10 +8369,8 @@
       <c r="C55">
         <v>4.013</v>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D55" t="s">
+        <v>51</v>
       </c>
       <c r="E55">
         <v>24</v>
@@ -7970,7 +8451,7 @@
         <v>10.2259984858831</v>
       </c>
       <c r="AE55">
-        <v>8.408212087526421</v>
+        <v>8.40821208752642</v>
       </c>
       <c r="AF55">
         <v>4.17134477173739</v>
@@ -8003,23 +8484,12 @@
         <v>1</v>
       </c>
       <c r="AP55">
-        <v>4</v>
-      </c>
-      <c r="AQ55">
-        <v>4</v>
-      </c>
-      <c r="AR55">
-        <v>0</v>
-      </c>
-      <c r="AS55">
         <v>8</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>T059</t>
-        </is>
+    <row r="56" spans="1:42">
+      <c r="A56" t="s">
+        <v>100</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -8027,10 +8497,8 @@
       <c r="C56">
         <v>0</v>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D56" t="s">
+        <v>45</v>
       </c>
       <c r="E56">
         <v>52</v>
@@ -8063,7 +8531,7 @@
         <v>5.2738564327458</v>
       </c>
       <c r="O56">
-        <v>8.782237660411271</v>
+        <v>8.78223766041127</v>
       </c>
       <c r="P56">
         <v>6.99990976413617</v>
@@ -8108,7 +8576,7 @@
         <v>5.33054509968904</v>
       </c>
       <c r="AD56">
-        <v>9.450131371385799</v>
+        <v>9.4501313713858</v>
       </c>
       <c r="AE56">
         <v>6.57307221058644</v>
@@ -8117,7 +8585,7 @@
         <v>5.77181634374121</v>
       </c>
       <c r="AG56">
-        <v>9.492557903549431</v>
+        <v>9.49255790354943</v>
       </c>
       <c r="AH56">
         <v>83</v>
@@ -8144,23 +8612,12 @@
         <v>12</v>
       </c>
       <c r="AP56">
-        <v>3</v>
-      </c>
-      <c r="AQ56">
-        <v>11</v>
-      </c>
-      <c r="AR56">
-        <v>2</v>
-      </c>
-      <c r="AS56">
         <v>16</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>T060</t>
-        </is>
+    <row r="57" spans="1:42">
+      <c r="A57" t="s">
+        <v>101</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -8168,10 +8625,8 @@
       <c r="C57">
         <v>1.882</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D57" t="s">
+        <v>48</v>
       </c>
       <c r="E57">
         <v>67</v>
@@ -8285,23 +8740,12 @@
         <v>8</v>
       </c>
       <c r="AP57">
-        <v>8</v>
-      </c>
-      <c r="AQ57">
-        <v>27</v>
-      </c>
-      <c r="AR57">
-        <v>22</v>
-      </c>
-      <c r="AS57">
         <v>57</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>T061</t>
-        </is>
+    <row r="58" spans="1:42">
+      <c r="A58" t="s">
+        <v>102</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -8309,10 +8753,8 @@
       <c r="C58">
         <v>3.346</v>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D58" t="s">
+        <v>51</v>
       </c>
       <c r="E58">
         <v>53</v>
@@ -8426,23 +8868,12 @@
         <v>8</v>
       </c>
       <c r="AP58">
-        <v>3</v>
-      </c>
-      <c r="AQ58">
-        <v>5</v>
-      </c>
-      <c r="AR58">
-        <v>0</v>
-      </c>
-      <c r="AS58">
         <v>8</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>T062</t>
-        </is>
+    <row r="59" spans="1:42">
+      <c r="A59" t="s">
+        <v>103</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -8450,10 +8881,8 @@
       <c r="C59">
         <v>3.253</v>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D59" t="s">
+        <v>48</v>
       </c>
       <c r="E59">
         <v>64</v>
@@ -8498,7 +8927,7 @@
         <v>4.52647676069399</v>
       </c>
       <c r="S59">
-        <v>8.692848206555629</v>
+        <v>8.69284820655563</v>
       </c>
       <c r="T59">
         <v>5.27043563364733</v>
@@ -8567,23 +8996,12 @@
         <v>17</v>
       </c>
       <c r="AP59">
-        <v>5</v>
-      </c>
-      <c r="AQ59">
-        <v>12</v>
-      </c>
-      <c r="AR59">
-        <v>1</v>
-      </c>
-      <c r="AS59">
         <v>18</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>T064</t>
-        </is>
+    <row r="60" spans="1:42">
+      <c r="A60" t="s">
+        <v>104</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -8591,10 +9009,8 @@
       <c r="C60">
         <v>1.349</v>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D60" t="s">
+        <v>43</v>
       </c>
       <c r="E60">
         <v>61</v>
@@ -8636,7 +9052,7 @@
         <v>5.06590375239863</v>
       </c>
       <c r="R60">
-        <v>8.369281538004969</v>
+        <v>8.36928153800497</v>
       </c>
       <c r="S60">
         <v>4.69328127401863</v>
@@ -8708,23 +9124,12 @@
         <v>79</v>
       </c>
       <c r="AP60">
-        <v>5</v>
-      </c>
-      <c r="AQ60">
-        <v>24</v>
-      </c>
-      <c r="AR60">
-        <v>7</v>
-      </c>
-      <c r="AS60">
         <v>36</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>T065</t>
-        </is>
+    <row r="61" spans="1:42">
+      <c r="A61" t="s">
+        <v>105</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -8732,10 +9137,8 @@
       <c r="C61">
         <v>3.382</v>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D61" t="s">
+        <v>51</v>
       </c>
       <c r="E61">
         <v>63</v>
@@ -8849,23 +9252,12 @@
         <v>18</v>
       </c>
       <c r="AP61">
-        <v>9</v>
-      </c>
-      <c r="AQ61">
-        <v>17</v>
-      </c>
-      <c r="AR61">
-        <v>3</v>
-      </c>
-      <c r="AS61">
         <v>29</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>T066</t>
-        </is>
+    <row r="62" spans="1:42">
+      <c r="A62" t="s">
+        <v>106</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -8873,10 +9265,8 @@
       <c r="C62">
         <v>2.77</v>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D62" t="s">
+        <v>48</v>
       </c>
       <c r="E62">
         <v>52</v>
@@ -8990,23 +9380,12 @@
         <v>7</v>
       </c>
       <c r="AP62">
-        <v>7</v>
-      </c>
-      <c r="AQ62">
-        <v>18</v>
-      </c>
-      <c r="AR62">
-        <v>2</v>
-      </c>
-      <c r="AS62">
         <v>27</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>T067</t>
-        </is>
+    <row r="63" spans="1:42">
+      <c r="A63" t="s">
+        <v>107</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -9014,10 +9393,8 @@
       <c r="C63">
         <v>2.966</v>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D63" t="s">
+        <v>48</v>
       </c>
       <c r="E63">
         <v>48</v>
@@ -9131,23 +9508,12 @@
         <v>9</v>
       </c>
       <c r="AP63">
-        <v>2</v>
-      </c>
-      <c r="AQ63">
-        <v>26</v>
-      </c>
-      <c r="AR63">
-        <v>7</v>
-      </c>
-      <c r="AS63">
         <v>35</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>T068</t>
-        </is>
+    <row r="64" spans="1:42">
+      <c r="A64" t="s">
+        <v>108</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -9155,10 +9521,8 @@
       <c r="C64">
         <v>3.591</v>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D64" t="s">
+        <v>51</v>
       </c>
       <c r="E64">
         <v>61</v>
@@ -9272,23 +9636,12 @@
         <v>10</v>
       </c>
       <c r="AP64">
-        <v>4</v>
-      </c>
-      <c r="AQ64">
-        <v>17</v>
-      </c>
-      <c r="AR64">
-        <v>8</v>
-      </c>
-      <c r="AS64">
         <v>29</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>T069</t>
-        </is>
+    <row r="65" spans="1:42">
+      <c r="A65" t="s">
+        <v>109</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -9296,10 +9649,8 @@
       <c r="C65">
         <v>1.062</v>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D65" t="s">
+        <v>43</v>
       </c>
       <c r="E65">
         <v>65</v>
@@ -9353,23 +9704,12 @@
         <v>17</v>
       </c>
       <c r="AP65">
-        <v>6</v>
-      </c>
-      <c r="AQ65">
-        <v>9</v>
-      </c>
-      <c r="AR65">
-        <v>1</v>
-      </c>
-      <c r="AS65">
         <v>16</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>T070</t>
-        </is>
+    <row r="66" spans="1:42">
+      <c r="A66" t="s">
+        <v>110</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -9377,10 +9717,8 @@
       <c r="C66">
         <v>0</v>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D66" t="s">
+        <v>45</v>
       </c>
       <c r="E66">
         <v>63</v>
@@ -9428,10 +9766,10 @@
         <v>4.17134477173739</v>
       </c>
       <c r="T66">
-        <v>9.124045134893739</v>
+        <v>9.12404513489374</v>
       </c>
       <c r="U66">
-        <v>8.860619445750499</v>
+        <v>8.8606194457505</v>
       </c>
       <c r="V66">
         <v>4.7916006575814</v>
@@ -9494,23 +9832,12 @@
         <v>8</v>
       </c>
       <c r="AP66">
-        <v>6</v>
-      </c>
-      <c r="AQ66">
-        <v>20</v>
-      </c>
-      <c r="AR66">
-        <v>3</v>
-      </c>
-      <c r="AS66">
         <v>29</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>T071</t>
-        </is>
+    <row r="67" spans="1:42">
+      <c r="A67" t="s">
+        <v>111</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -9518,10 +9845,8 @@
       <c r="C67">
         <v>0</v>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D67" t="s">
+        <v>45</v>
       </c>
       <c r="E67">
         <v>35</v>
@@ -9635,23 +9960,12 @@
         <v>17</v>
       </c>
       <c r="AP67">
-        <v>21</v>
-      </c>
-      <c r="AQ67">
-        <v>30</v>
-      </c>
-      <c r="AR67">
-        <v>21</v>
-      </c>
-      <c r="AS67">
         <v>72</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>T072</t>
-        </is>
+    <row r="68" spans="1:42">
+      <c r="A68" t="s">
+        <v>112</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -9659,10 +9973,8 @@
       <c r="C68">
         <v>3.152</v>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D68" t="s">
+        <v>48</v>
       </c>
       <c r="E68">
         <v>53</v>
@@ -9698,7 +10010,7 @@
         <v>5.9026799822774</v>
       </c>
       <c r="P68">
-        <v>8.537679696693679</v>
+        <v>8.53767969669368</v>
       </c>
       <c r="Q68">
         <v>6.34051125800205</v>
@@ -9740,7 +10052,7 @@
         <v>5.82523950137466</v>
       </c>
       <c r="AD68">
-        <v>8.167340491718051</v>
+        <v>8.16734049171805</v>
       </c>
       <c r="AE68">
         <v>6.35804422365756</v>
@@ -9776,23 +10088,12 @@
         <v>6</v>
       </c>
       <c r="AP68">
-        <v>6</v>
-      </c>
-      <c r="AQ68">
-        <v>21</v>
-      </c>
-      <c r="AR68">
-        <v>0</v>
-      </c>
-      <c r="AS68">
         <v>27</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>T073</t>
-        </is>
+    <row r="69" spans="1:42">
+      <c r="A69" t="s">
+        <v>113</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -9800,10 +10101,8 @@
       <c r="C69">
         <v>0</v>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D69" t="s">
+        <v>45</v>
       </c>
       <c r="E69">
         <v>38</v>
@@ -9845,7 +10144,7 @@
         <v>6.80378447754732</v>
       </c>
       <c r="R69">
-        <v>8.580136545008219</v>
+        <v>8.58013654500822</v>
       </c>
       <c r="S69">
         <v>5.84287357692568</v>
@@ -9917,23 +10216,12 @@
         <v>4</v>
       </c>
       <c r="AP69">
-        <v>5</v>
-      </c>
-      <c r="AQ69">
-        <v>5</v>
-      </c>
-      <c r="AR69">
-        <v>2</v>
-      </c>
-      <c r="AS69">
         <v>12</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>T074</t>
-        </is>
+    <row r="70" spans="1:42">
+      <c r="A70" t="s">
+        <v>114</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -9941,10 +10229,8 @@
       <c r="C70">
         <v>1.45</v>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D70" t="s">
+        <v>48</v>
       </c>
       <c r="E70">
         <v>50</v>
@@ -10022,7 +10308,7 @@
         <v>4.64636254360634</v>
       </c>
       <c r="AD70">
-        <v>8.013964874581321</v>
+        <v>8.01396487458132</v>
       </c>
       <c r="AE70">
         <v>6.85823048000306</v>
@@ -10058,23 +10344,12 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>5</v>
-      </c>
-      <c r="AQ70">
-        <v>8</v>
-      </c>
-      <c r="AR70">
-        <v>0</v>
-      </c>
-      <c r="AS70">
         <v>13</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>T075</t>
-        </is>
+    <row r="71" spans="1:42">
+      <c r="A71" t="s">
+        <v>115</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -10082,10 +10357,8 @@
       <c r="C71">
         <v>1.169</v>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D71" t="s">
+        <v>43</v>
       </c>
       <c r="E71">
         <v>52</v>
@@ -10139,23 +10412,12 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>9</v>
-      </c>
-      <c r="AQ71">
-        <v>28</v>
-      </c>
-      <c r="AR71">
-        <v>26</v>
-      </c>
-      <c r="AS71">
         <v>63</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>T076</t>
-        </is>
+    <row r="72" spans="1:42">
+      <c r="A72" t="s">
+        <v>116</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -10163,10 +10425,8 @@
       <c r="C72">
         <v>0.892</v>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D72" t="s">
+        <v>43</v>
       </c>
       <c r="E72">
         <v>54</v>
@@ -10280,23 +10540,12 @@
         <v>3</v>
       </c>
       <c r="AP72">
-        <v>7</v>
-      </c>
-      <c r="AQ72">
-        <v>5</v>
-      </c>
-      <c r="AR72">
-        <v>0</v>
-      </c>
-      <c r="AS72">
         <v>12</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>T077</t>
-        </is>
+    <row r="73" spans="1:42">
+      <c r="A73" t="s">
+        <v>117</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -10304,10 +10553,8 @@
       <c r="C73">
         <v>0</v>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D73" t="s">
+        <v>45</v>
       </c>
       <c r="E73">
         <v>48</v>
@@ -10361,23 +10608,12 @@
         <v>0</v>
       </c>
       <c r="AP73">
-        <v>4</v>
-      </c>
-      <c r="AQ73">
-        <v>8</v>
-      </c>
-      <c r="AR73">
-        <v>0</v>
-      </c>
-      <c r="AS73">
         <v>12</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>T078</t>
-        </is>
+    <row r="74" spans="1:42">
+      <c r="A74" t="s">
+        <v>118</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -10385,10 +10621,8 @@
       <c r="C74">
         <v>1.491</v>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D74" t="s">
+        <v>48</v>
       </c>
       <c r="E74">
         <v>50</v>
@@ -10469,7 +10703,7 @@
         <v>7.4521920461295</v>
       </c>
       <c r="AE74">
-        <v>8.288759676769009</v>
+        <v>8.28875967676901</v>
       </c>
       <c r="AF74">
         <v>6.10036404350097</v>
@@ -10502,23 +10736,12 @@
         <v>21</v>
       </c>
       <c r="AP74">
-        <v>10</v>
-      </c>
-      <c r="AQ74">
-        <v>21</v>
-      </c>
-      <c r="AR74">
-        <v>2</v>
-      </c>
-      <c r="AS74">
         <v>33</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>T079</t>
-        </is>
+    <row r="75" spans="1:42">
+      <c r="A75" t="s">
+        <v>119</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -10526,10 +10749,8 @@
       <c r="C75">
         <v>0</v>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D75" t="s">
+        <v>45</v>
       </c>
       <c r="E75">
         <v>59</v>
@@ -10643,23 +10864,12 @@
         <v>23</v>
       </c>
       <c r="AP75">
-        <v>6</v>
-      </c>
-      <c r="AQ75">
-        <v>21</v>
-      </c>
-      <c r="AR75">
-        <v>3</v>
-      </c>
-      <c r="AS75">
         <v>30</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>T080</t>
-        </is>
+    <row r="76" spans="1:42">
+      <c r="A76" t="s">
+        <v>120</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -10667,10 +10877,8 @@
       <c r="C76">
         <v>1.72</v>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D76" t="s">
+        <v>48</v>
       </c>
       <c r="E76">
         <v>50</v>
@@ -10784,23 +10992,12 @@
         <v>4</v>
       </c>
       <c r="AP76">
-        <v>0</v>
-      </c>
-      <c r="AQ76">
-        <v>16</v>
-      </c>
-      <c r="AR76">
-        <v>11</v>
-      </c>
-      <c r="AS76">
         <v>27</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>T081</t>
-        </is>
+    <row r="77" spans="1:42">
+      <c r="A77" t="s">
+        <v>121</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -10808,10 +11005,8 @@
       <c r="C77">
         <v>0</v>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D77" t="s">
+        <v>45</v>
       </c>
       <c r="E77">
         <v>39</v>
@@ -10925,34 +11120,21 @@
         <v>33</v>
       </c>
       <c r="AP77">
-        <v>24</v>
-      </c>
-      <c r="AQ77">
-        <v>29</v>
-      </c>
-      <c r="AR77">
-        <v>27</v>
-      </c>
-      <c r="AS77">
         <v>80</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>T083</t>
-        </is>
+    <row r="78" spans="1:42">
+      <c r="A78" t="s">
+        <v>122</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+        <v>0.558</v>
+      </c>
+      <c r="D78" t="s">
+        <v>43</v>
       </c>
       <c r="E78">
         <v>48</v>
@@ -11066,23 +11248,12 @@
         <v>20</v>
       </c>
       <c r="AP78">
-        <v>6</v>
-      </c>
-      <c r="AQ78">
-        <v>14</v>
-      </c>
-      <c r="AR78">
-        <v>5</v>
-      </c>
-      <c r="AS78">
         <v>25</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>T086</t>
-        </is>
+    <row r="79" spans="1:42">
+      <c r="A79" t="s">
+        <v>123</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -11090,10 +11261,8 @@
       <c r="C79">
         <v>2.129</v>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D79" t="s">
+        <v>48</v>
       </c>
       <c r="E79">
         <v>63</v>
@@ -11207,23 +11376,12 @@
         <v>13</v>
       </c>
       <c r="AP79">
-        <v>4</v>
-      </c>
-      <c r="AQ79">
-        <v>7</v>
-      </c>
-      <c r="AR79">
-        <v>4</v>
-      </c>
-      <c r="AS79">
         <v>15</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>T087</t>
-        </is>
+    <row r="80" spans="1:42">
+      <c r="A80" t="s">
+        <v>124</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -11231,10 +11389,8 @@
       <c r="C80">
         <v>2.553</v>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D80" t="s">
+        <v>48</v>
       </c>
       <c r="E80">
         <v>56</v>
@@ -11348,23 +11504,12 @@
         <v>10</v>
       </c>
       <c r="AP80">
-        <v>10</v>
-      </c>
-      <c r="AQ80">
-        <v>11</v>
-      </c>
-      <c r="AR80">
-        <v>0</v>
-      </c>
-      <c r="AS80">
         <v>21</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>T089</t>
-        </is>
+    <row r="81" spans="1:42">
+      <c r="A81" t="s">
+        <v>125</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -11372,10 +11517,8 @@
       <c r="C81">
         <v>3.165</v>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D81" t="s">
+        <v>48</v>
       </c>
       <c r="E81">
         <v>33</v>
@@ -11489,23 +11632,12 @@
         <v>3</v>
       </c>
       <c r="AP81">
-        <v>11</v>
-      </c>
-      <c r="AQ81">
-        <v>19</v>
-      </c>
-      <c r="AR81">
-        <v>1</v>
-      </c>
-      <c r="AS81">
         <v>31</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>T090</t>
-        </is>
+    <row r="82" spans="1:42">
+      <c r="A82" t="s">
+        <v>126</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -11513,10 +11645,8 @@
       <c r="C82">
         <v>1.414</v>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D82" t="s">
+        <v>48</v>
       </c>
       <c r="E82">
         <v>49</v>
@@ -11630,23 +11760,12 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>9</v>
-      </c>
-      <c r="AQ82">
-        <v>9</v>
-      </c>
-      <c r="AR82">
-        <v>0</v>
-      </c>
-      <c r="AS82">
         <v>18</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>T091</t>
-        </is>
+    <row r="83" spans="1:42">
+      <c r="A83" t="s">
+        <v>127</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -11654,10 +11773,8 @@
       <c r="C83">
         <v>1.86</v>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D83" t="s">
+        <v>48</v>
       </c>
       <c r="E83">
         <v>45</v>
@@ -11711,23 +11828,12 @@
         <v>0</v>
       </c>
       <c r="AP83">
-        <v>4</v>
-      </c>
-      <c r="AQ83">
-        <v>7</v>
-      </c>
-      <c r="AR83">
-        <v>1</v>
-      </c>
-      <c r="AS83">
         <v>12</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>T092</t>
-        </is>
+    <row r="84" spans="1:42">
+      <c r="A84" t="s">
+        <v>128</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -11735,10 +11841,8 @@
       <c r="C84">
         <v>1.169</v>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D84" t="s">
+        <v>43</v>
       </c>
       <c r="E84">
         <v>53</v>
@@ -11852,23 +11956,12 @@
         <v>15</v>
       </c>
       <c r="AP84">
-        <v>10</v>
-      </c>
-      <c r="AQ84">
-        <v>17</v>
-      </c>
-      <c r="AR84">
-        <v>3</v>
-      </c>
-      <c r="AS84">
         <v>30</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>T093</t>
-        </is>
+    <row r="85" spans="1:42">
+      <c r="A85" t="s">
+        <v>129</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -11876,10 +11969,8 @@
       <c r="C85">
         <v>2.636</v>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D85" t="s">
+        <v>48</v>
       </c>
       <c r="E85">
         <v>48</v>
@@ -11939,7 +12030,7 @@
         <v>5.40507792514331</v>
       </c>
       <c r="X85">
-        <v>8.238502435088691</v>
+        <v>8.23850243508869</v>
       </c>
       <c r="Y85">
         <v>4.6676837509772</v>
@@ -11957,7 +12048,7 @@
         <v>4.8698969340334</v>
       </c>
       <c r="AD85">
-        <v>8.907191514620649</v>
+        <v>8.90719151462065</v>
       </c>
       <c r="AE85">
         <v>6.46528459853728</v>
@@ -11993,23 +12084,12 @@
         <v>6</v>
       </c>
       <c r="AP85">
-        <v>10</v>
-      </c>
-      <c r="AQ85">
-        <v>22</v>
-      </c>
-      <c r="AR85">
-        <v>8</v>
-      </c>
-      <c r="AS85">
         <v>40</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>T094</t>
-        </is>
+    <row r="86" spans="1:42">
+      <c r="A86" t="s">
+        <v>130</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -12017,10 +12097,8 @@
       <c r="C86">
         <v>0</v>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D86" t="s">
+        <v>45</v>
       </c>
       <c r="E86">
         <v>35</v>
@@ -12068,10 +12146,10 @@
         <v>4.60262573466854</v>
       </c>
       <c r="T86">
-        <v>9.368289685905079</v>
+        <v>9.36828968590508</v>
       </c>
       <c r="U86">
-        <v>9.087454983120081</v>
+        <v>9.08745498312008</v>
       </c>
       <c r="V86">
         <v>5.6378754817875</v>
@@ -12134,23 +12212,12 @@
         <v>12</v>
       </c>
       <c r="AP86">
-        <v>23</v>
-      </c>
-      <c r="AQ86">
-        <v>32</v>
-      </c>
-      <c r="AR86">
-        <v>32</v>
-      </c>
-      <c r="AS86">
         <v>87</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>T095</t>
-        </is>
+    <row r="87" spans="1:42">
+      <c r="A87" t="s">
+        <v>131</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -12158,10 +12225,8 @@
       <c r="C87">
         <v>0</v>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D87" t="s">
+        <v>45</v>
       </c>
       <c r="E87">
         <v>53</v>
@@ -12230,7 +12295,7 @@
         <v>5.50974174513818</v>
       </c>
       <c r="AA87">
-        <v>8.230091644215181</v>
+        <v>8.23009164421518</v>
       </c>
       <c r="AB87">
         <v>6.0064842516909</v>
@@ -12248,7 +12313,7 @@
         <v>5.66469378849341</v>
       </c>
       <c r="AG87">
-        <v>8.488952618726319</v>
+        <v>8.48895261872632</v>
       </c>
       <c r="AH87">
         <v>29</v>
@@ -12275,23 +12340,12 @@
         <v>13</v>
       </c>
       <c r="AP87">
-        <v>7</v>
-      </c>
-      <c r="AQ87">
-        <v>14</v>
-      </c>
-      <c r="AR87">
-        <v>0</v>
-      </c>
-      <c r="AS87">
         <v>21</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>T096</t>
-        </is>
+    <row r="88" spans="1:42">
+      <c r="A88" t="s">
+        <v>132</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -12299,10 +12353,8 @@
       <c r="C88">
         <v>3.869</v>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D88" t="s">
+        <v>51</v>
       </c>
       <c r="E88">
         <v>59</v>
@@ -12380,7 +12432,7 @@
         <v>5.91096528815923</v>
       </c>
       <c r="AD88">
-        <v>8.506001268255851</v>
+        <v>8.50600126825585</v>
       </c>
       <c r="AE88">
         <v>7.17744517945359</v>
@@ -12416,23 +12468,12 @@
         <v>7</v>
       </c>
       <c r="AP88">
-        <v>5</v>
-      </c>
-      <c r="AQ88">
-        <v>9</v>
-      </c>
-      <c r="AR88">
-        <v>0</v>
-      </c>
-      <c r="AS88">
         <v>14</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>T097</t>
-        </is>
+    <row r="89" spans="1:42">
+      <c r="A89" t="s">
+        <v>133</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -12440,10 +12481,8 @@
       <c r="C89">
         <v>0</v>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D89" t="s">
+        <v>45</v>
       </c>
       <c r="E89">
         <v>56</v>
@@ -12557,23 +12596,12 @@
         <v>15</v>
       </c>
       <c r="AP89">
-        <v>10</v>
-      </c>
-      <c r="AQ89">
-        <v>15</v>
-      </c>
-      <c r="AR89">
-        <v>5</v>
-      </c>
-      <c r="AS89">
         <v>30</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>T098</t>
-        </is>
+    <row r="90" spans="1:42">
+      <c r="A90" t="s">
+        <v>134</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -12581,10 +12609,8 @@
       <c r="C90">
         <v>3.105</v>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D90" t="s">
+        <v>48</v>
       </c>
       <c r="E90">
         <v>37</v>
@@ -12620,7 +12646,7 @@
         <v>6.04105122651373</v>
       </c>
       <c r="P90">
-        <v>8.671016234154269</v>
+        <v>8.67101623415427</v>
       </c>
       <c r="Q90">
         <v>7.54400720296085</v>
@@ -12698,23 +12724,12 @@
         <v>3</v>
       </c>
       <c r="AP90">
-        <v>4</v>
-      </c>
-      <c r="AQ90">
-        <v>9</v>
-      </c>
-      <c r="AR90">
-        <v>6</v>
-      </c>
-      <c r="AS90">
         <v>19</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>T099</t>
-        </is>
+    <row r="91" spans="1:42">
+      <c r="A91" t="s">
+        <v>135</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -12722,10 +12737,8 @@
       <c r="C91">
         <v>0</v>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D91" t="s">
+        <v>45</v>
       </c>
       <c r="E91">
         <v>62</v>
@@ -12839,23 +12852,12 @@
         <v>6</v>
       </c>
       <c r="AP91">
-        <v>6</v>
-      </c>
-      <c r="AQ91">
-        <v>12</v>
-      </c>
-      <c r="AR91">
-        <v>1</v>
-      </c>
-      <c r="AS91">
         <v>19</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>T100</t>
-        </is>
+    <row r="92" spans="1:42">
+      <c r="A92" t="s">
+        <v>136</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -12863,10 +12865,8 @@
       <c r="C92">
         <v>0.892</v>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D92" t="s">
+        <v>43</v>
       </c>
       <c r="E92">
         <v>57</v>
@@ -12980,23 +12980,12 @@
         <v>9</v>
       </c>
       <c r="AP92">
-        <v>6</v>
-      </c>
-      <c r="AQ92">
-        <v>15</v>
-      </c>
-      <c r="AR92">
-        <v>1</v>
-      </c>
-      <c r="AS92">
         <v>22</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>T101</t>
-        </is>
+    <row r="93" spans="1:42">
+      <c r="A93" t="s">
+        <v>137</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -13004,10 +12993,8 @@
       <c r="C93">
         <v>3.225</v>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D93" t="s">
+        <v>48</v>
       </c>
       <c r="E93">
         <v>74</v>
@@ -13058,7 +13045,7 @@
         <v>4.92332086745619</v>
       </c>
       <c r="U93">
-        <v>8.793984777331691</v>
+        <v>8.79398477733169</v>
       </c>
       <c r="V93">
         <v>4.65013794015682</v>
@@ -13121,23 +13108,12 @@
         <v>14</v>
       </c>
       <c r="AP93">
-        <v>7</v>
-      </c>
-      <c r="AQ93">
-        <v>7</v>
-      </c>
-      <c r="AR93">
-        <v>2</v>
-      </c>
-      <c r="AS93">
         <v>16</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>T102</t>
-        </is>
+    <row r="94" spans="1:42">
+      <c r="A94" t="s">
+        <v>138</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -13145,10 +13121,8 @@
       <c r="C94">
         <v>3.679</v>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D94" t="s">
+        <v>51</v>
       </c>
       <c r="E94">
         <v>65</v>
@@ -13202,23 +13176,12 @@
         <v>4</v>
       </c>
       <c r="AP94">
-        <v>5</v>
-      </c>
-      <c r="AQ94">
-        <v>7</v>
-      </c>
-      <c r="AR94">
-        <v>3</v>
-      </c>
-      <c r="AS94">
         <v>15</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>T103</t>
-        </is>
+    <row r="95" spans="1:42">
+      <c r="A95" t="s">
+        <v>139</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -13226,10 +13189,8 @@
       <c r="C95">
         <v>0</v>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D95" t="s">
+        <v>45</v>
       </c>
       <c r="E95">
         <v>55</v>
@@ -13280,7 +13241,7 @@
         <v>4.84158173540966</v>
       </c>
       <c r="U95">
-        <v>8.738882183811119</v>
+        <v>8.73888218381112</v>
       </c>
       <c r="V95">
         <v>7.10789953620772</v>
@@ -13343,23 +13304,12 @@
         <v>4</v>
       </c>
       <c r="AP95">
-        <v>21</v>
-      </c>
-      <c r="AQ95">
-        <v>19</v>
-      </c>
-      <c r="AR95">
-        <v>13</v>
-      </c>
-      <c r="AS95">
         <v>53</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>T104</t>
-        </is>
+    <row r="96" spans="1:42">
+      <c r="A96" t="s">
+        <v>140</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -13367,10 +13317,8 @@
       <c r="C96">
         <v>0</v>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D96" t="s">
+        <v>45</v>
       </c>
       <c r="E96">
         <v>53</v>
@@ -13484,23 +13432,12 @@
         <v>12</v>
       </c>
       <c r="AP96">
-        <v>6</v>
-      </c>
-      <c r="AQ96">
-        <v>15</v>
-      </c>
-      <c r="AR96">
-        <v>3</v>
-      </c>
-      <c r="AS96">
         <v>24</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>T105</t>
-        </is>
+    <row r="97" spans="1:42">
+      <c r="A97" t="s">
+        <v>141</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -13508,10 +13445,8 @@
       <c r="C97">
         <v>1.028</v>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D97" t="s">
+        <v>43</v>
       </c>
       <c r="E97">
         <v>43</v>
@@ -13547,7 +13482,7 @@
         <v>4.99021532517972</v>
       </c>
       <c r="P97">
-        <v>8.247993497678079</v>
+        <v>8.24799349767808</v>
       </c>
       <c r="Q97">
         <v>5.50012210802015</v>
@@ -13625,23 +13560,12 @@
         <v>9</v>
       </c>
       <c r="AP97">
-        <v>7</v>
-      </c>
-      <c r="AQ97">
-        <v>19</v>
-      </c>
-      <c r="AR97">
-        <v>10</v>
-      </c>
-      <c r="AS97">
         <v>36</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>T109</t>
-        </is>
+    <row r="98" spans="1:42">
+      <c r="A98" t="s">
+        <v>142</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -13649,10 +13573,8 @@
       <c r="C98">
         <v>4.116</v>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D98" t="s">
+        <v>51</v>
       </c>
       <c r="E98">
         <v>39</v>
@@ -13766,23 +13688,12 @@
         <v>1</v>
       </c>
       <c r="AP98">
-        <v>6</v>
-      </c>
-      <c r="AQ98">
-        <v>11</v>
-      </c>
-      <c r="AR98">
-        <v>1</v>
-      </c>
-      <c r="AS98">
         <v>18</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>T110</t>
-        </is>
+    <row r="99" spans="1:42">
+      <c r="A99" t="s">
+        <v>143</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -13790,10 +13701,8 @@
       <c r="C99">
         <v>2.913</v>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D99" t="s">
+        <v>48</v>
       </c>
       <c r="E99">
         <v>42</v>
@@ -13907,23 +13816,12 @@
         <v>3</v>
       </c>
       <c r="AP99">
-        <v>7</v>
-      </c>
-      <c r="AQ99">
-        <v>12</v>
-      </c>
-      <c r="AR99">
-        <v>0</v>
-      </c>
-      <c r="AS99">
         <v>19</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>T112</t>
-        </is>
+    <row r="100" spans="1:42">
+      <c r="A100" t="s">
+        <v>144</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -13931,10 +13829,8 @@
       <c r="C100">
         <v>0</v>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D100" t="s">
+        <v>45</v>
       </c>
       <c r="E100">
         <v>38</v>
@@ -14048,23 +13944,12 @@
         <v>1</v>
       </c>
       <c r="AP100">
-        <v>6</v>
-      </c>
-      <c r="AQ100">
-        <v>19</v>
-      </c>
-      <c r="AR100">
-        <v>1</v>
-      </c>
-      <c r="AS100">
         <v>26</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>T114</t>
-        </is>
+    <row r="101" spans="1:42">
+      <c r="A101" t="s">
+        <v>145</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -14072,10 +13957,8 @@
       <c r="C101">
         <v>1.807</v>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D101" t="s">
+        <v>48</v>
       </c>
       <c r="E101">
         <v>62</v>
@@ -14126,7 +14009,7 @@
         <v>4.72920395382635</v>
       </c>
       <c r="U101">
-        <v>8.784060696005261</v>
+        <v>8.78406069600526</v>
       </c>
       <c r="V101">
         <v>4.62777201421979</v>
@@ -14189,23 +14072,12 @@
         <v>11</v>
       </c>
       <c r="AP101">
-        <v>5</v>
-      </c>
-      <c r="AQ101">
-        <v>18</v>
-      </c>
-      <c r="AR101">
-        <v>0</v>
-      </c>
-      <c r="AS101">
         <v>23</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>T115</t>
-        </is>
+    <row r="102" spans="1:42">
+      <c r="A102" t="s">
+        <v>146</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -14213,10 +14085,8 @@
       <c r="C102">
         <v>3.68</v>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D102" t="s">
+        <v>51</v>
       </c>
       <c r="E102">
         <v>56</v>
@@ -14330,23 +14200,12 @@
         <v>10</v>
       </c>
       <c r="AP102">
-        <v>9</v>
-      </c>
-      <c r="AQ102">
-        <v>27</v>
-      </c>
-      <c r="AR102">
-        <v>10</v>
-      </c>
-      <c r="AS102">
         <v>46</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>T116</t>
-        </is>
+    <row r="103" spans="1:42">
+      <c r="A103" t="s">
+        <v>147</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -14354,10 +14213,8 @@
       <c r="C103">
         <v>3.374</v>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D103" t="s">
+        <v>51</v>
       </c>
       <c r="E103">
         <v>66</v>
@@ -14471,23 +14328,12 @@
         <v>5</v>
       </c>
       <c r="AP103">
-        <v>3</v>
-      </c>
-      <c r="AQ103">
-        <v>10</v>
-      </c>
-      <c r="AR103">
-        <v>1</v>
-      </c>
-      <c r="AS103">
         <v>14</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>T117</t>
-        </is>
+    <row r="104" spans="1:42">
+      <c r="A104" t="s">
+        <v>148</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -14495,10 +14341,8 @@
       <c r="C104">
         <v>0.911</v>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D104" t="s">
+        <v>43</v>
       </c>
       <c r="E104">
         <v>59</v>
@@ -14576,7 +14420,7 @@
         <v>4.17134477173739</v>
       </c>
       <c r="AD104">
-        <v>8.360431109768051</v>
+        <v>8.36043110976805</v>
       </c>
       <c r="AE104">
         <v>7.01227627007367</v>
@@ -14612,23 +14456,12 @@
         <v>7</v>
       </c>
       <c r="AP104">
-        <v>5</v>
-      </c>
-      <c r="AQ104">
-        <v>22</v>
-      </c>
-      <c r="AR104">
-        <v>0</v>
-      </c>
-      <c r="AS104">
         <v>27</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>T118</t>
-        </is>
+    <row r="105" spans="1:42">
+      <c r="A105" t="s">
+        <v>149</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -14636,10 +14469,8 @@
       <c r="C105">
         <v>3.041</v>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D105" t="s">
+        <v>48</v>
       </c>
       <c r="E105">
         <v>44</v>
@@ -14753,23 +14584,12 @@
         <v>1</v>
       </c>
       <c r="AP105">
-        <v>19</v>
-      </c>
-      <c r="AQ105">
-        <v>17</v>
-      </c>
-      <c r="AR105">
-        <v>9</v>
-      </c>
-      <c r="AS105">
         <v>45</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>T119</t>
-        </is>
+    <row r="106" spans="1:42">
+      <c r="A106" t="s">
+        <v>150</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -14777,10 +14597,8 @@
       <c r="C106">
         <v>2.398</v>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D106" t="s">
+        <v>48</v>
       </c>
       <c r="E106">
         <v>52</v>
@@ -14894,23 +14712,12 @@
         <v>6</v>
       </c>
       <c r="AP106">
-        <v>6</v>
-      </c>
-      <c r="AQ106">
-        <v>8</v>
-      </c>
-      <c r="AR106">
-        <v>9</v>
-      </c>
-      <c r="AS106">
         <v>23</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>T120</t>
-        </is>
+    <row r="107" spans="1:42">
+      <c r="A107" t="s">
+        <v>151</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -14918,10 +14725,8 @@
       <c r="C107">
         <v>1.023</v>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D107" t="s">
+        <v>43</v>
       </c>
       <c r="E107">
         <v>61</v>
@@ -15035,23 +14840,12 @@
         <v>13</v>
       </c>
       <c r="AP107">
-        <v>4</v>
-      </c>
-      <c r="AQ107">
-        <v>7</v>
-      </c>
-      <c r="AR107">
-        <v>0</v>
-      </c>
-      <c r="AS107">
         <v>11</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>T121</t>
-        </is>
+    <row r="108" spans="1:42">
+      <c r="A108" t="s">
+        <v>152</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -15059,10 +14853,8 @@
       <c r="C108">
         <v>3.114</v>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D108" t="s">
+        <v>48</v>
       </c>
       <c r="E108">
         <v>50</v>
@@ -15176,23 +14968,12 @@
         <v>0</v>
       </c>
       <c r="AP108">
-        <v>6</v>
-      </c>
-      <c r="AQ108">
-        <v>7</v>
-      </c>
-      <c r="AR108">
-        <v>8</v>
-      </c>
-      <c r="AS108">
         <v>21</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>T122</t>
-        </is>
+    <row r="109" spans="1:42">
+      <c r="A109" t="s">
+        <v>153</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -15200,10 +14981,8 @@
       <c r="C109">
         <v>3.015</v>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D109" t="s">
+        <v>48</v>
       </c>
       <c r="E109">
         <v>55</v>
@@ -15257,23 +15036,12 @@
         <v>7</v>
       </c>
       <c r="AP109">
-        <v>9</v>
-      </c>
-      <c r="AQ109">
-        <v>8</v>
-      </c>
-      <c r="AR109">
-        <v>0</v>
-      </c>
-      <c r="AS109">
         <v>17</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>T123</t>
-        </is>
+    <row r="110" spans="1:42">
+      <c r="A110" t="s">
+        <v>154</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -15281,10 +15049,8 @@
       <c r="C110">
         <v>1.98</v>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D110" t="s">
+        <v>48</v>
       </c>
       <c r="E110">
         <v>53</v>
@@ -15398,23 +15164,12 @@
         <v>9</v>
       </c>
       <c r="AP110">
-        <v>11</v>
-      </c>
-      <c r="AQ110">
-        <v>27</v>
-      </c>
-      <c r="AR110">
-        <v>13</v>
-      </c>
-      <c r="AS110">
         <v>51</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>T124</t>
-        </is>
+    <row r="111" spans="1:42">
+      <c r="A111" t="s">
+        <v>155</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -15422,10 +15177,8 @@
       <c r="C111">
         <v>3.055</v>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D111" t="s">
+        <v>48</v>
       </c>
       <c r="E111">
         <v>50</v>
@@ -15539,23 +15292,12 @@
         <v>10</v>
       </c>
       <c r="AP111">
-        <v>4</v>
-      </c>
-      <c r="AQ111">
-        <v>14</v>
-      </c>
-      <c r="AR111">
-        <v>0</v>
-      </c>
-      <c r="AS111">
         <v>18</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>T125</t>
-        </is>
+    <row r="112" spans="1:42">
+      <c r="A112" t="s">
+        <v>156</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -15563,10 +15305,8 @@
       <c r="C112">
         <v>1.125</v>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D112" t="s">
+        <v>43</v>
       </c>
       <c r="E112">
         <v>56</v>
@@ -15680,23 +15420,12 @@
         <v>14</v>
       </c>
       <c r="AP112">
-        <v>11</v>
-      </c>
-      <c r="AQ112">
-        <v>19</v>
-      </c>
-      <c r="AR112">
-        <v>20</v>
-      </c>
-      <c r="AS112">
         <v>50</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>T126</t>
-        </is>
+    <row r="113" spans="1:42">
+      <c r="A113" t="s">
+        <v>157</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -15704,10 +15433,8 @@
       <c r="C113">
         <v>1.687</v>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D113" t="s">
+        <v>48</v>
       </c>
       <c r="E113">
         <v>32</v>
@@ -15821,23 +15548,12 @@
         <v>8</v>
       </c>
       <c r="AP113">
-        <v>8</v>
-      </c>
-      <c r="AQ113">
-        <v>10</v>
-      </c>
-      <c r="AR113">
-        <v>2</v>
-      </c>
-      <c r="AS113">
         <v>20</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>T127</t>
-        </is>
+    <row r="114" spans="1:42">
+      <c r="A114" t="s">
+        <v>158</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -15845,10 +15561,8 @@
       <c r="C114">
         <v>3.597</v>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D114" t="s">
+        <v>51</v>
       </c>
       <c r="E114">
         <v>65</v>
@@ -15962,23 +15676,12 @@
         <v>75</v>
       </c>
       <c r="AP114">
-        <v>4</v>
-      </c>
-      <c r="AQ114">
-        <v>5</v>
-      </c>
-      <c r="AR114">
-        <v>0</v>
-      </c>
-      <c r="AS114">
         <v>9</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>T128</t>
-        </is>
+    <row r="115" spans="1:42">
+      <c r="A115" t="s">
+        <v>159</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -15986,10 +15689,8 @@
       <c r="C115">
         <v>0</v>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D115" t="s">
+        <v>45</v>
       </c>
       <c r="E115">
         <v>55</v>
@@ -16103,23 +15804,12 @@
         <v>11</v>
       </c>
       <c r="AP115">
-        <v>1</v>
-      </c>
-      <c r="AQ115">
-        <v>26</v>
-      </c>
-      <c r="AR115">
-        <v>9</v>
-      </c>
-      <c r="AS115">
         <v>36</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>T129</t>
-        </is>
+    <row r="116" spans="1:42">
+      <c r="A116" t="s">
+        <v>160</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -16127,10 +15817,8 @@
       <c r="C116">
         <v>1.729</v>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D116" t="s">
+        <v>48</v>
       </c>
       <c r="E116">
         <v>43</v>
@@ -16211,7 +15899,7 @@
         <v>5.34753997161099</v>
       </c>
       <c r="AE116">
-        <v>8.699133070540951</v>
+        <v>8.69913307054095</v>
       </c>
       <c r="AF116">
         <v>7.19937402484065</v>
@@ -16238,29 +15926,18 @@
         <v>0</v>
       </c>
       <c r="AN116">
-        <v>0.6782224890205421</v>
+        <v>0.678222489020542</v>
       </c>
       <c r="AO116">
         <v>11</v>
       </c>
       <c r="AP116">
-        <v>10</v>
-      </c>
-      <c r="AQ116">
-        <v>21</v>
-      </c>
-      <c r="AR116">
-        <v>2</v>
-      </c>
-      <c r="AS116">
         <v>33</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>T130</t>
-        </is>
+    <row r="117" spans="1:42">
+      <c r="A117" t="s">
+        <v>161</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -16268,10 +15945,8 @@
       <c r="C117">
         <v>1.623</v>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D117" t="s">
+        <v>48</v>
       </c>
       <c r="E117">
         <v>68</v>
@@ -16322,7 +15997,7 @@
         <v>5.65708293855645</v>
       </c>
       <c r="U117">
-        <v>8.218022063842049</v>
+        <v>8.21802206384205</v>
       </c>
       <c r="V117">
         <v>4.7875574687791</v>
@@ -16385,23 +16060,12 @@
         <v>10</v>
       </c>
       <c r="AP117">
-        <v>9</v>
-      </c>
-      <c r="AQ117">
-        <v>31</v>
-      </c>
-      <c r="AR117">
-        <v>19</v>
-      </c>
-      <c r="AS117">
         <v>59</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>T131</t>
-        </is>
+    <row r="118" spans="1:42">
+      <c r="A118" t="s">
+        <v>162</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -16409,10 +16073,8 @@
       <c r="C118">
         <v>4.074</v>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D118" t="s">
+        <v>51</v>
       </c>
       <c r="E118">
         <v>81</v>
@@ -16472,7 +16134,7 @@
         <v>4.47701485090498</v>
       </c>
       <c r="X118">
-        <v>9.038318112048961</v>
+        <v>9.03831811204896</v>
       </c>
       <c r="Y118">
         <v>6.10123472861511</v>
@@ -16526,23 +16188,12 @@
         <v>11</v>
       </c>
       <c r="AP118">
-        <v>7</v>
-      </c>
-      <c r="AQ118">
-        <v>10</v>
-      </c>
-      <c r="AR118">
-        <v>0</v>
-      </c>
-      <c r="AS118">
         <v>17</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>T132</t>
-        </is>
+    <row r="119" spans="1:42">
+      <c r="A119" t="s">
+        <v>163</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -16550,10 +16201,8 @@
       <c r="C119">
         <v>1.54</v>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D119" t="s">
+        <v>48</v>
       </c>
       <c r="E119">
         <v>47</v>
@@ -16667,23 +16316,12 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>3</v>
-      </c>
-      <c r="AQ119">
-        <v>4</v>
-      </c>
-      <c r="AR119">
-        <v>0</v>
-      </c>
-      <c r="AS119">
         <v>7</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>T133</t>
-        </is>
+    <row r="120" spans="1:42">
+      <c r="A120" t="s">
+        <v>164</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -16691,10 +16329,8 @@
       <c r="C120">
         <v>3.259</v>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D120" t="s">
+        <v>48</v>
       </c>
       <c r="E120">
         <v>61</v>
@@ -16808,23 +16444,12 @@
         <v>40</v>
       </c>
       <c r="AP120">
-        <v>8</v>
-      </c>
-      <c r="AQ120">
-        <v>24</v>
-      </c>
-      <c r="AR120">
-        <v>2</v>
-      </c>
-      <c r="AS120">
         <v>34</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>T134</t>
-        </is>
+    <row r="121" spans="1:42">
+      <c r="A121" t="s">
+        <v>165</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -16832,10 +16457,8 @@
       <c r="C121">
         <v>2.834</v>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D121" t="s">
+        <v>48</v>
       </c>
       <c r="E121">
         <v>36</v>
@@ -16949,23 +16572,12 @@
         <v>5</v>
       </c>
       <c r="AP121">
-        <v>14</v>
-      </c>
-      <c r="AQ121">
-        <v>17</v>
-      </c>
-      <c r="AR121">
-        <v>7</v>
-      </c>
-      <c r="AS121">
         <v>38</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>T135</t>
-        </is>
+    <row r="122" spans="1:42">
+      <c r="A122" t="s">
+        <v>166</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -16973,10 +16585,8 @@
       <c r="C122">
         <v>0</v>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D122" t="s">
+        <v>45</v>
       </c>
       <c r="E122">
         <v>41</v>
@@ -17027,7 +16637,7 @@
         <v>5.87776505976536</v>
       </c>
       <c r="U122">
-        <v>8.140517037104971</v>
+        <v>8.14051703710497</v>
       </c>
       <c r="V122">
         <v>5.49127670344164</v>
@@ -17084,29 +16694,18 @@
         <v>0</v>
       </c>
       <c r="AN122">
-        <v>0.5477887419455429</v>
+        <v>0.547788741945543</v>
       </c>
       <c r="AO122">
         <v>17</v>
       </c>
       <c r="AP122">
-        <v>10</v>
-      </c>
-      <c r="AQ122">
-        <v>21</v>
-      </c>
-      <c r="AR122">
-        <v>2</v>
-      </c>
-      <c r="AS122">
         <v>33</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>T136</t>
-        </is>
+    <row r="123" spans="1:42">
+      <c r="A123" t="s">
+        <v>167</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -17114,10 +16713,8 @@
       <c r="C123">
         <v>0</v>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D123" t="s">
+        <v>45</v>
       </c>
       <c r="E123">
         <v>67</v>
@@ -17231,23 +16828,12 @@
         <v>27</v>
       </c>
       <c r="AP123">
-        <v>5</v>
-      </c>
-      <c r="AQ123">
-        <v>25</v>
-      </c>
-      <c r="AR123">
-        <v>3</v>
-      </c>
-      <c r="AS123">
         <v>33</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>T137</t>
-        </is>
+    <row r="124" spans="1:42">
+      <c r="A124" t="s">
+        <v>168</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -17255,10 +16841,8 @@
       <c r="C124">
         <v>2.545</v>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D124" t="s">
+        <v>48</v>
       </c>
       <c r="E124">
         <v>45</v>
@@ -17294,7 +16878,7 @@
         <v>4.62137903603101</v>
       </c>
       <c r="P124">
-        <v>8.779608810086531</v>
+        <v>8.77960881008653</v>
       </c>
       <c r="Q124">
         <v>7.12064046439725</v>
@@ -17372,23 +16956,12 @@
         <v>4</v>
       </c>
       <c r="AP124">
-        <v>1</v>
-      </c>
-      <c r="AQ124">
-        <v>3</v>
-      </c>
-      <c r="AR124">
-        <v>1</v>
-      </c>
-      <c r="AS124">
         <v>5</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>T138</t>
-        </is>
+    <row r="125" spans="1:42">
+      <c r="A125" t="s">
+        <v>169</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -17396,10 +16969,8 @@
       <c r="C125">
         <v>1.568</v>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D125" t="s">
+        <v>48</v>
       </c>
       <c r="E125">
         <v>38</v>
@@ -17450,7 +17021,7 @@
         <v>5.30564506484576</v>
       </c>
       <c r="U125">
-        <v>8.530108918862719</v>
+        <v>8.53010891886272</v>
       </c>
       <c r="V125">
         <v>5.37502682828549</v>
@@ -17477,7 +17048,7 @@
         <v>5.19088022299115</v>
       </c>
       <c r="AD125">
-        <v>8.365039470122261</v>
+        <v>8.36503947012226</v>
       </c>
       <c r="AE125">
         <v>7.38335647104861</v>
@@ -17513,23 +17084,12 @@
         <v>8</v>
       </c>
       <c r="AP125">
-        <v>9</v>
-      </c>
-      <c r="AQ125">
-        <v>10</v>
-      </c>
-      <c r="AR125">
-        <v>2</v>
-      </c>
-      <c r="AS125">
         <v>21</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>T139</t>
-        </is>
+    <row r="126" spans="1:42">
+      <c r="A126" t="s">
+        <v>170</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -17537,10 +17097,8 @@
       <c r="C126">
         <v>3.055</v>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D126" t="s">
+        <v>48</v>
       </c>
       <c r="E126">
         <v>46</v>
@@ -17654,23 +17212,12 @@
         <v>13</v>
       </c>
       <c r="AP126">
-        <v>13</v>
-      </c>
-      <c r="AQ126">
-        <v>16</v>
-      </c>
-      <c r="AR126">
-        <v>3</v>
-      </c>
-      <c r="AS126">
         <v>32</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>T140</t>
-        </is>
+    <row r="127" spans="1:42">
+      <c r="A127" t="s">
+        <v>171</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -17678,10 +17225,8 @@
       <c r="C127">
         <v>3.753</v>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D127" t="s">
+        <v>51</v>
       </c>
       <c r="E127">
         <v>47</v>
@@ -17795,23 +17340,12 @@
         <v>5</v>
       </c>
       <c r="AP127">
-        <v>2</v>
-      </c>
-      <c r="AQ127">
-        <v>10</v>
-      </c>
-      <c r="AR127">
-        <v>0</v>
-      </c>
-      <c r="AS127">
         <v>12</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>T141</t>
-        </is>
+    <row r="128" spans="1:42">
+      <c r="A128" t="s">
+        <v>172</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -17819,10 +17353,8 @@
       <c r="C128">
         <v>1.799</v>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D128" t="s">
+        <v>48</v>
       </c>
       <c r="E128">
         <v>39</v>
@@ -17936,23 +17468,12 @@
         <v>6</v>
       </c>
       <c r="AP128">
-        <v>3</v>
-      </c>
-      <c r="AQ128">
-        <v>7</v>
-      </c>
-      <c r="AR128">
-        <v>0</v>
-      </c>
-      <c r="AS128">
         <v>10</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>T142</t>
-        </is>
+    <row r="129" spans="1:42">
+      <c r="A129" t="s">
+        <v>173</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -17960,10 +17481,8 @@
       <c r="C129">
         <v>0</v>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D129" t="s">
+        <v>45</v>
       </c>
       <c r="E129">
         <v>42</v>
@@ -18077,23 +17596,12 @@
         <v>4</v>
       </c>
       <c r="AP129">
-        <v>7</v>
-      </c>
-      <c r="AQ129">
-        <v>9</v>
-      </c>
-      <c r="AR129">
-        <v>6</v>
-      </c>
-      <c r="AS129">
         <v>22</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>T143</t>
-        </is>
+    <row r="130" spans="1:42">
+      <c r="A130" t="s">
+        <v>174</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -18101,10 +17609,8 @@
       <c r="C130">
         <v>0</v>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D130" t="s">
+        <v>45</v>
       </c>
       <c r="E130">
         <v>49</v>
@@ -18155,7 +17661,7 @@
         <v>7.55608052058541</v>
       </c>
       <c r="U130">
-        <v>9.707722661977551</v>
+        <v>9.70772266197755</v>
       </c>
       <c r="V130">
         <v>6.41546908644749</v>
@@ -18218,23 +17724,12 @@
         <v>26</v>
       </c>
       <c r="AP130">
-        <v>9</v>
-      </c>
-      <c r="AQ130">
-        <v>26</v>
-      </c>
-      <c r="AR130">
-        <v>25</v>
-      </c>
-      <c r="AS130">
         <v>60</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>T144</t>
-        </is>
+    <row r="131" spans="1:42">
+      <c r="A131" t="s">
+        <v>175</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -18242,10 +17737,8 @@
       <c r="C131">
         <v>0</v>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D131" t="s">
+        <v>45</v>
       </c>
       <c r="E131">
         <v>58</v>
@@ -18299,23 +17792,12 @@
         <v>36</v>
       </c>
       <c r="AP131">
-        <v>7</v>
-      </c>
-      <c r="AQ131">
-        <v>17</v>
-      </c>
-      <c r="AR131">
-        <v>1</v>
-      </c>
-      <c r="AS131">
         <v>25</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>T145</t>
-        </is>
+    <row r="132" spans="1:42">
+      <c r="A132" t="s">
+        <v>176</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -18323,10 +17805,8 @@
       <c r="C132">
         <v>3.712</v>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D132" t="s">
+        <v>51</v>
       </c>
       <c r="E132">
         <v>62</v>
@@ -18440,23 +17920,12 @@
         <v>3</v>
       </c>
       <c r="AP132">
-        <v>6</v>
-      </c>
-      <c r="AQ132">
-        <v>5</v>
-      </c>
-      <c r="AR132">
-        <v>4</v>
-      </c>
-      <c r="AS132">
         <v>15</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>T147</t>
-        </is>
+    <row r="133" spans="1:42">
+      <c r="A133" t="s">
+        <v>177</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -18464,10 +17933,8 @@
       <c r="C133">
         <v>2.16</v>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D133" t="s">
+        <v>48</v>
       </c>
       <c r="E133">
         <v>57</v>
@@ -18581,23 +18048,12 @@
         <v>16</v>
       </c>
       <c r="AP133">
-        <v>3</v>
-      </c>
-      <c r="AQ133">
-        <v>12</v>
-      </c>
-      <c r="AR133">
-        <v>4</v>
-      </c>
-      <c r="AS133">
         <v>19</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>T148</t>
-        </is>
+    <row r="134" spans="1:42">
+      <c r="A134" t="s">
+        <v>178</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -18605,10 +18061,8 @@
       <c r="C134">
         <v>3.022</v>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D134" t="s">
+        <v>48</v>
       </c>
       <c r="E134">
         <v>38</v>
@@ -18722,23 +18176,12 @@
         <v>12</v>
       </c>
       <c r="AP134">
-        <v>9</v>
-      </c>
-      <c r="AQ134">
-        <v>17</v>
-      </c>
-      <c r="AR134">
-        <v>11</v>
-      </c>
-      <c r="AS134">
         <v>37</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>T149</t>
-        </is>
+    <row r="135" spans="1:42">
+      <c r="A135" t="s">
+        <v>179</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -18746,10 +18189,8 @@
       <c r="C135">
         <v>1.143</v>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D135" t="s">
+        <v>43</v>
       </c>
       <c r="E135">
         <v>28</v>
@@ -18863,23 +18304,12 @@
         <v>1</v>
       </c>
       <c r="AP135">
-        <v>9</v>
-      </c>
-      <c r="AQ135">
-        <v>17</v>
-      </c>
-      <c r="AR135">
-        <v>3</v>
-      </c>
-      <c r="AS135">
         <v>29</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>T150</t>
-        </is>
+    <row r="136" spans="1:42">
+      <c r="A136" t="s">
+        <v>180</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -18887,10 +18317,8 @@
       <c r="C136">
         <v>3.796</v>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D136" t="s">
+        <v>51</v>
       </c>
       <c r="E136">
         <v>60</v>
@@ -19004,23 +18432,12 @@
         <v>14</v>
       </c>
       <c r="AP136">
-        <v>8</v>
-      </c>
-      <c r="AQ136">
-        <v>12</v>
-      </c>
-      <c r="AR136">
-        <v>1</v>
-      </c>
-      <c r="AS136">
         <v>21</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>T151</t>
-        </is>
+    <row r="137" spans="1:42">
+      <c r="A137" t="s">
+        <v>181</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -19028,10 +18445,8 @@
       <c r="C137">
         <v>2.685</v>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D137" t="s">
+        <v>48</v>
       </c>
       <c r="E137">
         <v>68</v>
@@ -19109,7 +18524,7 @@
         <v>4.61720719738744</v>
       </c>
       <c r="AD137">
-        <v>8.251268209448501</v>
+        <v>8.2512682094485</v>
       </c>
       <c r="AE137">
         <v>6.90764744293102</v>
@@ -19145,23 +18560,12 @@
         <v>18</v>
       </c>
       <c r="AP137">
-        <v>6</v>
-      </c>
-      <c r="AQ137">
-        <v>15</v>
-      </c>
-      <c r="AR137">
-        <v>0</v>
-      </c>
-      <c r="AS137">
         <v>21</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>T152</t>
-        </is>
+    <row r="138" spans="1:42">
+      <c r="A138" t="s">
+        <v>182</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -19169,10 +18573,8 @@
       <c r="C138">
         <v>0</v>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D138" t="s">
+        <v>45</v>
       </c>
       <c r="E138">
         <v>36</v>
@@ -19286,23 +18688,12 @@
         <v>41</v>
       </c>
       <c r="AP138">
-        <v>8</v>
-      </c>
-      <c r="AQ138">
-        <v>8</v>
-      </c>
-      <c r="AR138">
-        <v>0</v>
-      </c>
-      <c r="AS138">
         <v>16</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>T153</t>
-        </is>
+    <row r="139" spans="1:42">
+      <c r="A139" t="s">
+        <v>183</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -19310,10 +18701,8 @@
       <c r="C139">
         <v>1.878</v>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D139" t="s">
+        <v>48</v>
       </c>
       <c r="E139">
         <v>64</v>
@@ -19427,23 +18816,12 @@
         <v>9</v>
       </c>
       <c r="AP139">
-        <v>5</v>
-      </c>
-      <c r="AQ139">
-        <v>14</v>
-      </c>
-      <c r="AR139">
-        <v>2</v>
-      </c>
-      <c r="AS139">
         <v>21</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>T154</t>
-        </is>
+    <row r="140" spans="1:42">
+      <c r="A140" t="s">
+        <v>184</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -19451,10 +18829,8 @@
       <c r="C140">
         <v>0</v>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D140" t="s">
+        <v>45</v>
       </c>
       <c r="E140">
         <v>62</v>
@@ -19568,23 +18944,12 @@
         <v>14</v>
       </c>
       <c r="AP140">
-        <v>6</v>
-      </c>
-      <c r="AQ140">
-        <v>19</v>
-      </c>
-      <c r="AR140">
-        <v>0</v>
-      </c>
-      <c r="AS140">
         <v>25</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>T155</t>
-        </is>
+    <row r="141" spans="1:42">
+      <c r="A141" t="s">
+        <v>185</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -19592,10 +18957,8 @@
       <c r="C141">
         <v>3.144</v>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D141" t="s">
+        <v>48</v>
       </c>
       <c r="E141">
         <v>58</v>
@@ -19709,23 +19072,12 @@
         <v>5</v>
       </c>
       <c r="AP141">
-        <v>12</v>
-      </c>
-      <c r="AQ141">
-        <v>11</v>
-      </c>
-      <c r="AR141">
-        <v>2</v>
-      </c>
-      <c r="AS141">
         <v>25</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>T156</t>
-        </is>
+    <row r="142" spans="1:42">
+      <c r="A142" t="s">
+        <v>186</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -19733,10 +19085,8 @@
       <c r="C142">
         <v>3.65</v>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D142" t="s">
+        <v>51</v>
       </c>
       <c r="E142">
         <v>67</v>
@@ -19775,7 +19125,7 @@
         <v>5.63100778058466</v>
       </c>
       <c r="Q142">
-        <v>8.484983911774339</v>
+        <v>8.48498391177434</v>
       </c>
       <c r="R142">
         <v>4.51105062778089</v>
@@ -19850,23 +19200,12 @@
         <v>6</v>
       </c>
       <c r="AP142">
-        <v>4</v>
-      </c>
-      <c r="AQ142">
-        <v>9</v>
-      </c>
-      <c r="AR142">
-        <v>0</v>
-      </c>
-      <c r="AS142">
         <v>13</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>T159</t>
-        </is>
+    <row r="143" spans="1:42">
+      <c r="A143" t="s">
+        <v>187</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -19874,10 +19213,8 @@
       <c r="C143">
         <v>3.477</v>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D143" t="s">
+        <v>51</v>
       </c>
       <c r="E143">
         <v>36</v>
@@ -19991,23 +19328,12 @@
         <v>2</v>
       </c>
       <c r="AP143">
-        <v>4</v>
-      </c>
-      <c r="AQ143">
-        <v>5</v>
-      </c>
-      <c r="AR143">
-        <v>1</v>
-      </c>
-      <c r="AS143">
         <v>10</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>T160</t>
-        </is>
+    <row r="144" spans="1:42">
+      <c r="A144" t="s">
+        <v>188</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -20015,10 +19341,8 @@
       <c r="C144">
         <v>2.187</v>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D144" t="s">
+        <v>48</v>
       </c>
       <c r="E144">
         <v>50</v>
@@ -20054,7 +19378,7 @@
         <v>5.67638369627672</v>
       </c>
       <c r="P144">
-        <v>8.506840094812651</v>
+        <v>8.50684009481265</v>
       </c>
       <c r="Q144">
         <v>6.35399194609995</v>
@@ -20132,23 +19456,12 @@
         <v>7</v>
       </c>
       <c r="AP144">
-        <v>7</v>
-      </c>
-      <c r="AQ144">
-        <v>12</v>
-      </c>
-      <c r="AR144">
-        <v>0</v>
-      </c>
-      <c r="AS144">
         <v>19</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>T161</t>
-        </is>
+    <row r="145" spans="1:42">
+      <c r="A145" t="s">
+        <v>189</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -20156,10 +19469,8 @@
       <c r="C145">
         <v>3.956</v>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D145" t="s">
+        <v>51</v>
       </c>
       <c r="E145">
         <v>55</v>
@@ -20195,7 +19506,7 @@
         <v>5.67435906342364</v>
       </c>
       <c r="P145">
-        <v>8.219822870640339</v>
+        <v>8.21982287064034</v>
       </c>
       <c r="Q145">
         <v>6.97175728926491</v>
@@ -20273,23 +19584,12 @@
         <v>9</v>
       </c>
       <c r="AP145">
-        <v>4</v>
-      </c>
-      <c r="AQ145">
-        <v>11</v>
-      </c>
-      <c r="AR145">
-        <v>5</v>
-      </c>
-      <c r="AS145">
         <v>20</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>T162</t>
-        </is>
+    <row r="146" spans="1:42">
+      <c r="A146" t="s">
+        <v>190</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -20297,10 +19597,8 @@
       <c r="C146">
         <v>0</v>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D146" t="s">
+        <v>45</v>
       </c>
       <c r="E146">
         <v>55</v>
@@ -20414,23 +19712,12 @@
         <v>7</v>
       </c>
       <c r="AP146">
-        <v>1</v>
-      </c>
-      <c r="AQ146">
-        <v>11</v>
-      </c>
-      <c r="AR146">
-        <v>1</v>
-      </c>
-      <c r="AS146">
         <v>13</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>T163</t>
-        </is>
+    <row r="147" spans="1:42">
+      <c r="A147" t="s">
+        <v>191</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -20438,10 +19725,8 @@
       <c r="C147">
         <v>0</v>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D147" t="s">
+        <v>45</v>
       </c>
       <c r="E147">
         <v>39</v>
@@ -20495,34 +19780,21 @@
         <v>0</v>
       </c>
       <c r="AP147">
-        <v>5</v>
-      </c>
-      <c r="AQ147">
-        <v>11</v>
-      </c>
-      <c r="AR147">
-        <v>1</v>
-      </c>
-      <c r="AS147">
         <v>17</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>T164</t>
-        </is>
+    <row r="148" spans="1:42">
+      <c r="A148" t="s">
+        <v>192</v>
       </c>
       <c r="B148">
         <v>0</v>
       </c>
       <c r="C148">
-        <v>0.9429999999999999</v>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+        <v>0.943</v>
+      </c>
+      <c r="D148" t="s">
+        <v>43</v>
       </c>
       <c r="E148">
         <v>44</v>
@@ -20636,23 +19908,12 @@
         <v>8</v>
       </c>
       <c r="AP148">
-        <v>12</v>
-      </c>
-      <c r="AQ148">
-        <v>14</v>
-      </c>
-      <c r="AR148">
-        <v>1</v>
-      </c>
-      <c r="AS148">
         <v>27</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>T166</t>
-        </is>
+    <row r="149" spans="1:42">
+      <c r="A149" t="s">
+        <v>193</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -20660,10 +19921,8 @@
       <c r="C149">
         <v>1.842</v>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D149" t="s">
+        <v>48</v>
       </c>
       <c r="E149">
         <v>48</v>
@@ -20777,23 +20036,12 @@
         <v>7</v>
       </c>
       <c r="AP149">
-        <v>6</v>
-      </c>
-      <c r="AQ149">
-        <v>5</v>
-      </c>
-      <c r="AR149">
-        <v>0</v>
-      </c>
-      <c r="AS149">
         <v>11</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>T167</t>
-        </is>
+    <row r="150" spans="1:42">
+      <c r="A150" t="s">
+        <v>194</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -20801,10 +20049,8 @@
       <c r="C150">
         <v>4.743</v>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D150" t="s">
+        <v>51</v>
       </c>
       <c r="E150">
         <v>59</v>
@@ -20858,23 +20104,12 @@
         <v>7</v>
       </c>
       <c r="AP150">
-        <v>3</v>
-      </c>
-      <c r="AQ150">
-        <v>3</v>
-      </c>
-      <c r="AR150">
-        <v>2</v>
-      </c>
-      <c r="AS150">
         <v>8</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>T168</t>
-        </is>
+    <row r="151" spans="1:42">
+      <c r="A151" t="s">
+        <v>195</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -20882,10 +20117,8 @@
       <c r="C151">
         <v>1.665</v>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D151" t="s">
+        <v>48</v>
       </c>
       <c r="E151">
         <v>50</v>
@@ -20993,29 +20226,18 @@
         <v>0</v>
       </c>
       <c r="AN151">
-        <v>0.5666058821964181</v>
+        <v>0.566605882196418</v>
       </c>
       <c r="AO151">
         <v>20</v>
       </c>
       <c r="AP151">
-        <v>9</v>
-      </c>
-      <c r="AQ151">
-        <v>27</v>
-      </c>
-      <c r="AR151">
-        <v>1</v>
-      </c>
-      <c r="AS151">
         <v>37</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>T169</t>
-        </is>
+    <row r="152" spans="1:42">
+      <c r="A152" t="s">
+        <v>196</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -21023,10 +20245,8 @@
       <c r="C152">
         <v>2.036</v>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D152" t="s">
+        <v>48</v>
       </c>
       <c r="E152">
         <v>35</v>
@@ -21140,23 +20360,12 @@
         <v>6</v>
       </c>
       <c r="AP152">
-        <v>2</v>
-      </c>
-      <c r="AQ152">
-        <v>4</v>
-      </c>
-      <c r="AR152">
-        <v>1</v>
-      </c>
-      <c r="AS152">
         <v>7</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>T170</t>
-        </is>
+    <row r="153" spans="1:42">
+      <c r="A153" t="s">
+        <v>197</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -21164,10 +20373,8 @@
       <c r="C153">
         <v>0.899</v>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D153" t="s">
+        <v>43</v>
       </c>
       <c r="E153">
         <v>66</v>
@@ -21281,23 +20488,12 @@
         <v>2</v>
       </c>
       <c r="AP153">
-        <v>4</v>
-      </c>
-      <c r="AQ153">
-        <v>9</v>
-      </c>
-      <c r="AR153">
-        <v>2</v>
-      </c>
-      <c r="AS153">
         <v>15</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>T171</t>
-        </is>
+    <row r="154" spans="1:42">
+      <c r="A154" t="s">
+        <v>198</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -21305,10 +20501,8 @@
       <c r="C154">
         <v>3.164</v>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D154" t="s">
+        <v>48</v>
       </c>
       <c r="E154">
         <v>68</v>
@@ -21422,23 +20616,12 @@
         <v>8</v>
       </c>
       <c r="AP154">
-        <v>4</v>
-      </c>
-      <c r="AQ154">
-        <v>11</v>
-      </c>
-      <c r="AR154">
-        <v>0</v>
-      </c>
-      <c r="AS154">
         <v>15</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>T172</t>
-        </is>
+    <row r="155" spans="1:42">
+      <c r="A155" t="s">
+        <v>199</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -21446,10 +20629,8 @@
       <c r="C155">
         <v>0</v>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D155" t="s">
+        <v>45</v>
       </c>
       <c r="E155">
         <v>54</v>
@@ -21518,7 +20699,7 @@
         <v>5.30989114728976</v>
       </c>
       <c r="AA155">
-        <v>9.050461011413971</v>
+        <v>9.05046101141397</v>
       </c>
       <c r="AB155">
         <v>4.75158741877921</v>
@@ -21563,23 +20744,12 @@
         <v>12</v>
       </c>
       <c r="AP155">
-        <v>6</v>
-      </c>
-      <c r="AQ155">
-        <v>21</v>
-      </c>
-      <c r="AR155">
-        <v>10</v>
-      </c>
-      <c r="AS155">
         <v>37</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>T173</t>
-        </is>
+    <row r="156" spans="1:42">
+      <c r="A156" t="s">
+        <v>200</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -21587,10 +20757,8 @@
       <c r="C156">
         <v>1.52</v>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>RCB-II</t>
-        </is>
+      <c r="D156" t="s">
+        <v>48</v>
       </c>
       <c r="E156">
         <v>68</v>
@@ -21704,23 +20872,12 @@
         <v>16</v>
       </c>
       <c r="AP156">
-        <v>2</v>
-      </c>
-      <c r="AQ156">
-        <v>8</v>
-      </c>
-      <c r="AR156">
-        <v>0</v>
-      </c>
-      <c r="AS156">
         <v>10</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>T174</t>
-        </is>
+    <row r="157" spans="1:42">
+      <c r="A157" t="s">
+        <v>201</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -21728,10 +20885,8 @@
       <c r="C157">
         <v>3.352</v>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D157" t="s">
+        <v>51</v>
       </c>
       <c r="E157">
         <v>50</v>
@@ -21794,7 +20949,7 @@
         <v>5.32695574579641</v>
       </c>
       <c r="Y157">
-        <v>8.161093514551821</v>
+        <v>8.16109351455182</v>
       </c>
       <c r="Z157">
         <v>5.02947750292576</v>
@@ -21845,23 +21000,12 @@
         <v>8</v>
       </c>
       <c r="AP157">
-        <v>2</v>
-      </c>
-      <c r="AQ157">
-        <v>4</v>
-      </c>
-      <c r="AR157">
-        <v>0</v>
-      </c>
-      <c r="AS157">
         <v>6</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>T175</t>
-        </is>
+    <row r="158" spans="1:42">
+      <c r="A158" t="s">
+        <v>202</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -21869,10 +21013,8 @@
       <c r="C158">
         <v>1.204</v>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>RCB-I</t>
-        </is>
+      <c r="D158" t="s">
+        <v>43</v>
       </c>
       <c r="E158">
         <v>48</v>
@@ -21908,7 +21050,7 @@
         <v>6.17859284953608</v>
       </c>
       <c r="P158">
-        <v>9.082140195874169</v>
+        <v>9.08214019587417</v>
       </c>
       <c r="Q158">
         <v>6.41892270851396</v>
@@ -21986,23 +21128,12 @@
         <v>9</v>
       </c>
       <c r="AP158">
-        <v>4</v>
-      </c>
-      <c r="AQ158">
-        <v>9</v>
-      </c>
-      <c r="AR158">
-        <v>0</v>
-      </c>
-      <c r="AS158">
         <v>13</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>T176</t>
-        </is>
+    <row r="159" spans="1:42">
+      <c r="A159" t="s">
+        <v>203</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -22010,10 +21141,8 @@
       <c r="C159">
         <v>4.255</v>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D159" t="s">
+        <v>51</v>
       </c>
       <c r="E159">
         <v>39</v>
@@ -22127,23 +21256,12 @@
         <v>14</v>
       </c>
       <c r="AP159">
-        <v>9</v>
-      </c>
-      <c r="AQ159">
-        <v>15</v>
-      </c>
-      <c r="AR159">
-        <v>2</v>
-      </c>
-      <c r="AS159">
         <v>26</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>T178</t>
-        </is>
+    <row r="160" spans="1:42">
+      <c r="A160" t="s">
+        <v>204</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -22151,10 +21269,8 @@
       <c r="C160">
         <v>3.523</v>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>RCB-III</t>
-        </is>
+      <c r="D160" t="s">
+        <v>51</v>
       </c>
       <c r="E160">
         <v>56</v>
@@ -22268,23 +21384,12 @@
         <v>9</v>
       </c>
       <c r="AP160">
-        <v>5</v>
-      </c>
-      <c r="AQ160">
-        <v>6</v>
-      </c>
-      <c r="AR160">
-        <v>2</v>
-      </c>
-      <c r="AS160">
         <v>13</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>T180</t>
-        </is>
+    <row r="161" spans="1:42">
+      <c r="A161" t="s">
+        <v>205</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -22292,10 +21397,8 @@
       <c r="C161">
         <v>0</v>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>pCR</t>
-        </is>
+      <c r="D161" t="s">
+        <v>45</v>
       </c>
       <c r="E161">
         <v>52</v>
@@ -22409,19 +21512,11 @@
         <v>15</v>
       </c>
       <c r="AP161">
-        <v>8</v>
-      </c>
-      <c r="AQ161">
-        <v>24</v>
-      </c>
-      <c r="AR161">
-        <v>2</v>
-      </c>
-      <c r="AS161">
         <v>34</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>